--- a/Курс 3/МиИМ/ИД23-1_Маслов АН_Задание-1.xlsx
+++ b/Курс 3/МиИМ/ИД23-1_Маслов АН_Задание-1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexm\Desktop\Рабочая папка\ITiABD\Курс 3\МиИМ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexm\OneDrive\Рабочий стол\ИТиАБД\ITiABD\Курс 3\МиИМ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE83C1D-79F1-432B-A80E-C7C37E4B3214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC357A9-423E-4B54-AD1A-A1651BE09188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3855" yWindow="3855" windowWidth="21600" windowHeight="11295" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Станд.норм.распр." sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="3." sheetId="5" r:id="rId5"/>
     <sheet name="4." sheetId="6" r:id="rId6"/>
     <sheet name="5." sheetId="7" r:id="rId7"/>
+    <sheet name="Алгоритм действий" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1519,6 +1520,61 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B56272FA-6C8B-B7E4-6D92-284B62529499}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="571500"/>
+          <a:ext cx="22393275" cy="10582275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
@@ -1783,21 +1839,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K108"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="5" customWidth="1"/>
     <col min="2" max="2" width="14" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="5" customWidth="1"/>
-    <col min="6" max="7" width="13.88671875" style="5" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" style="5" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="13.109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="5" customWidth="1"/>
+    <col min="6" max="7" width="13.85546875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1832,7 +1888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -1845,7 +1901,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>111</v>
       </c>
@@ -1880,7 +1936,7 @@
         <v>-0.94664073913008906</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>112</v>
       </c>
@@ -1915,7 +1971,7 @@
         <v>0.70356463766074695</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>113</v>
       </c>
@@ -1950,7 +2006,7 @@
         <v>-0.70180135480768513</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>114</v>
       </c>
@@ -1985,7 +2041,7 @@
         <v>4.4192347559146597E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>115</v>
       </c>
@@ -2020,7 +2076,7 @@
         <v>1.5348496162914671</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>116</v>
       </c>
@@ -2055,7 +2111,7 @@
         <v>0.91711854111053981</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>117</v>
       </c>
@@ -2090,7 +2146,7 @@
         <v>0.19737854017876089</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>118</v>
       </c>
@@ -2125,7 +2181,7 @@
         <v>-1.1263500709901564</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>119</v>
       </c>
@@ -2160,7 +2216,7 @@
         <v>0.34276808946742698</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>120</v>
       </c>
@@ -2195,7 +2251,7 @@
         <v>-0.29367583920247853</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>121</v>
       </c>
@@ -2230,7 +2286,7 @@
         <v>-0.12536474969238043</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>122</v>
       </c>
@@ -2265,7 +2321,7 @@
         <v>-2.9954208002891392E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>123</v>
       </c>
@@ -2300,7 +2356,7 @@
         <v>-0.32513526093680412</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>124</v>
       </c>
@@ -2335,7 +2391,7 @@
         <v>1.1930342225241499</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>125</v>
       </c>
@@ -2370,7 +2426,7 @@
         <v>-0.13331077247858</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>126</v>
       </c>
@@ -2405,7 +2461,7 @@
         <v>-0.12582631825353019</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>127</v>
       </c>
@@ -2440,7 +2496,7 @@
         <v>0.41903376768459566</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>128</v>
       </c>
@@ -2475,7 +2531,7 @@
         <v>-0.68836015998385847</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>129</v>
       </c>
@@ -2510,7 +2566,7 @@
         <v>1.5862860891502299</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>130</v>
       </c>
@@ -2545,7 +2601,7 @@
         <v>0.76036712925997563</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>131</v>
       </c>
@@ -2580,7 +2636,7 @@
         <v>-1.0000826478062663</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>132</v>
       </c>
@@ -2615,7 +2671,7 @@
         <v>1.2054397302563302</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>133</v>
       </c>
@@ -2650,7 +2706,7 @@
         <v>-1.4177794582792558</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>134</v>
       </c>
@@ -2685,7 +2741,7 @@
         <v>1.2393502402119339</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>135</v>
       </c>
@@ -2720,7 +2776,7 @@
         <v>-0.71270505941356532</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>136</v>
       </c>
@@ -2755,7 +2811,7 @@
         <v>-0.1141916072811</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>137</v>
       </c>
@@ -2790,7 +2846,7 @@
         <v>0.49194113671546802</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>138</v>
       </c>
@@ -2825,7 +2881,7 @@
         <v>1.3014005162403919</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>139</v>
       </c>
@@ -2860,7 +2916,7 @@
         <v>-0.51198526307416614</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>140</v>
       </c>
@@ -2895,7 +2951,7 @@
         <v>-1.4302213457995094</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>141</v>
       </c>
@@ -2930,7 +2986,7 @@
         <v>-2.707711246330291</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>142</v>
       </c>
@@ -2965,7 +3021,7 @@
         <v>-2.3371740098809823E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>143</v>
       </c>
@@ -3000,7 +3056,7 @@
         <v>0.6156847121019382</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>144</v>
       </c>
@@ -3035,7 +3091,7 @@
         <v>1.1848123904201202</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>145</v>
       </c>
@@ -3070,7 +3126,7 @@
         <v>-0.30712158149981406</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>146</v>
       </c>
@@ -3105,7 +3161,7 @@
         <v>0.985680799203692</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>147</v>
       </c>
@@ -3140,7 +3196,7 @@
         <v>0.53453049986273982</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>148</v>
       </c>
@@ -3175,7 +3231,7 @@
         <v>0.2629803930176422</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>149</v>
       </c>
@@ -3210,7 +3266,7 @@
         <v>-0.67187556851422414</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>150</v>
       </c>
@@ -3245,7 +3301,7 @@
         <v>-0.68062490754527971</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>151</v>
       </c>
@@ -3280,7 +3336,7 @@
         <v>2.5589542929083109</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>152</v>
       </c>
@@ -3315,7 +3371,7 @@
         <v>-0.3129002834612038</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>153</v>
       </c>
@@ -3350,7 +3406,7 @@
         <v>-0.38469806895591319</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>154</v>
       </c>
@@ -3385,7 +3441,7 @@
         <v>0.27011424208467361</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>155</v>
       </c>
@@ -3420,7 +3476,7 @@
         <v>-0.8355755198863335</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>156</v>
       </c>
@@ -3455,7 +3511,7 @@
         <v>-1.0200869837717619</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>157</v>
       </c>
@@ -3490,7 +3546,7 @@
         <v>-1.3101953300065361</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>158</v>
       </c>
@@ -3525,7 +3581,7 @@
         <v>-0.3998172815045109</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>159</v>
       </c>
@@ -3560,7 +3616,7 @@
         <v>-5.6677436077734455E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>160</v>
       </c>
@@ -3595,7 +3651,7 @@
         <v>0.33571950552868657</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>161</v>
       </c>
@@ -3630,7 +3686,7 @@
         <v>-0.19683284335769713</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>162</v>
       </c>
@@ -3665,7 +3721,7 @@
         <v>-0.52768734551500995</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>163</v>
       </c>
@@ -3700,7 +3756,7 @@
         <v>-0.56003273130045272</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>164</v>
       </c>
@@ -3735,7 +3791,7 @@
         <v>-1.2370446711429395</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>165</v>
       </c>
@@ -3770,7 +3826,7 @@
         <v>1.0336952982470393</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>166</v>
       </c>
@@ -3805,7 +3861,7 @@
         <v>-7.6688593253493309E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>167</v>
       </c>
@@ -3840,7 +3896,7 @@
         <v>-0.75486241257749498</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>168</v>
       </c>
@@ -3875,7 +3931,7 @@
         <v>-0.96915300673572347</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>169</v>
       </c>
@@ -3910,7 +3966,7 @@
         <v>-0.64703124028165004</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>170</v>
       </c>
@@ -3945,7 +4001,7 @@
         <v>0.78626044341945089</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>171</v>
       </c>
@@ -3980,7 +4036,7 @@
         <v>-0.22742483452020679</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>172</v>
       </c>
@@ -4015,7 +4071,7 @@
         <v>0.23717007024970371</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>173</v>
       </c>
@@ -4050,7 +4106,7 @@
         <v>0.56325689001823775</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>174</v>
       </c>
@@ -4085,7 +4141,7 @@
         <v>-0.59063495427835733</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>175</v>
       </c>
@@ -4120,7 +4176,7 @@
         <v>2.8652493710978888E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>176</v>
       </c>
@@ -4155,7 +4211,7 @@
         <v>-0.13462226888805162</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>177</v>
       </c>
@@ -4190,7 +4246,7 @@
         <v>2.1310916054062545</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
         <v>178</v>
       </c>
@@ -4225,7 +4281,7 @@
         <v>-0.36521521199029</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>179</v>
       </c>
@@ -4260,7 +4316,7 @@
         <v>1.3919225239078514</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>180</v>
       </c>
@@ -4295,7 +4351,7 @@
         <v>0.4135279141337378</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>181</v>
       </c>
@@ -4330,7 +4386,7 @@
         <v>-0.68787585405516438</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>182</v>
       </c>
@@ -4365,7 +4421,7 @@
         <v>1.9027720554731786</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>183</v>
       </c>
@@ -4400,7 +4456,7 @@
         <v>-0.33645244204671998</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>184</v>
       </c>
@@ -4435,7 +4491,7 @@
         <v>-0.18126990855670999</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
         <v>185</v>
       </c>
@@ -4470,7 +4526,7 @@
         <v>0.13176645552448463</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
         <v>186</v>
       </c>
@@ -4505,7 +4561,7 @@
         <v>-0.94568349595647305</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>187</v>
       </c>
@@ -4540,7 +4596,7 @@
         <v>0.32763637136667967</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>188</v>
       </c>
@@ -4575,7 +4631,7 @@
         <v>0.20252855392755009</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>189</v>
       </c>
@@ -4610,7 +4666,7 @@
         <v>-9.5731138571863994E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>190</v>
       </c>
@@ -4645,7 +4701,7 @@
         <v>-0.3446773411706</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
         <v>191</v>
       </c>
@@ -4680,7 +4736,7 @@
         <v>-0.42239514389075</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
         <v>192</v>
       </c>
@@ -4715,7 +4771,7 @@
         <v>-0.31885065254755318</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>193</v>
       </c>
@@ -4750,7 +4806,7 @@
         <v>0.1918431280500954</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
         <v>194</v>
       </c>
@@ -4785,7 +4841,7 @@
         <v>-0.25135705072898418</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
         <v>195</v>
       </c>
@@ -4820,7 +4876,7 @@
         <v>-0.12226950679905001</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>196</v>
       </c>
@@ -4855,7 +4911,7 @@
         <v>-0.60049842431908473</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>197</v>
       </c>
@@ -4890,7 +4946,7 @@
         <v>0.14157308214635123</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
         <v>198</v>
       </c>
@@ -4925,7 +4981,7 @@
         <v>1.5274417819455266</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
         <v>199</v>
       </c>
@@ -4960,7 +5016,7 @@
         <v>-0.12544205674203113</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
         <v>200</v>
       </c>
@@ -4995,7 +5051,7 @@
         <v>-0.15100567907211371</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
         <v>201</v>
       </c>
@@ -5030,7 +5086,7 @@
         <v>1.2742293620249256</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
         <v>202</v>
       </c>
@@ -5065,7 +5121,7 @@
         <v>0.46816239773761481</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
         <v>203</v>
       </c>
@@ -5100,7 +5156,7 @@
         <v>-0.82100848178379005</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
         <v>204</v>
       </c>
@@ -5135,7 +5191,7 @@
         <v>1.0896042113017756</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
         <v>205</v>
       </c>
@@ -5170,7 +5226,7 @@
         <v>-0.67225755628896877</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
         <v>206</v>
       </c>
@@ -5205,7 +5261,7 @@
         <v>-0.40761960917734541</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
         <v>207</v>
       </c>
@@ -5240,7 +5296,7 @@
         <v>-0.91653646450140513</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>208</v>
       </c>
@@ -5275,7 +5331,7 @@
         <v>-0.89429022409603931</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>209</v>
       </c>
@@ -5310,7 +5366,7 @@
         <v>0.12544205674203113</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>210</v>
       </c>
@@ -5345,7 +5401,7 @@
         <v>0.32271381199999999</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E108"/>
     </row>
   </sheetData>
@@ -5357,21 +5413,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O102"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="4.88671875" customWidth="1"/>
-    <col min="4" max="4" width="3.109375" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" customWidth="1"/>
-    <col min="6" max="6" width="3.5546875" customWidth="1"/>
-    <col min="7" max="7" width="3.109375" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" customWidth="1"/>
+    <col min="4" max="4" width="3.140625" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="6" max="6" width="3.5703125" customWidth="1"/>
+    <col min="7" max="7" width="3.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" customWidth="1"/>
     <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -5388,7 +5444,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -5418,7 +5474,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -5448,7 +5504,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -5478,7 +5534,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
@@ -5502,7 +5558,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
         <v>15</v>
       </c>
@@ -5526,7 +5582,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
@@ -5547,7 +5603,7 @@
         <v>8594</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
@@ -5571,7 +5627,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C9" s="4" t="s">
         <v>18</v>
       </c>
@@ -5595,7 +5651,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C10" s="4" t="s">
         <v>19</v>
       </c>
@@ -5619,7 +5675,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C11" s="4" t="s">
         <v>20</v>
       </c>
@@ -5640,7 +5696,7 @@
         <v>8704</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
         <v>21</v>
       </c>
@@ -5661,7 +5717,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C13" s="4" t="s">
         <v>22</v>
       </c>
@@ -5682,7 +5738,7 @@
         <v>7549</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C14" s="4" t="s">
         <v>23</v>
       </c>
@@ -5712,7 +5768,7 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C15" s="4" t="s">
         <v>24</v>
       </c>
@@ -5742,7 +5798,7 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C16" s="4" t="s">
         <v>25</v>
       </c>
@@ -5772,7 +5828,7 @@
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C17" s="4" t="s">
         <v>26</v>
       </c>
@@ -5793,7 +5849,7 @@
         <v>7560</v>
       </c>
     </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" s="4" t="s">
         <v>27</v>
       </c>
@@ -5814,7 +5870,7 @@
         <v>8781</v>
       </c>
     </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" s="4" t="s">
         <v>28</v>
       </c>
@@ -5842,7 +5898,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="4" t="s">
         <v>29</v>
       </c>
@@ -5869,7 +5925,7 @@
         <v>3.363626373201746E-13</v>
       </c>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="4" t="s">
         <v>30</v>
       </c>
@@ -5896,7 +5952,7 @@
         <v>1.545385696938562E-12</v>
       </c>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C22" s="4" t="s">
         <v>31</v>
       </c>
@@ -5923,7 +5979,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C23" s="4" t="s">
         <v>32</v>
       </c>
@@ -5950,7 +6006,7 @@
         <v>2.3404526132562395E-22</v>
       </c>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C24" s="4" t="s">
         <v>33</v>
       </c>
@@ -5971,7 +6027,7 @@
         <v>7593</v>
       </c>
     </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C25" s="4" t="s">
         <v>34</v>
       </c>
@@ -5992,7 +6048,7 @@
         <v>3072</v>
       </c>
     </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C26" s="4" t="s">
         <v>35</v>
       </c>
@@ -6013,7 +6069,7 @@
         <v>7725</v>
       </c>
     </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C27" s="4" t="s">
         <v>36</v>
       </c>
@@ -6034,7 +6090,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C28" s="4" t="s">
         <v>37</v>
       </c>
@@ -6055,7 +6111,7 @@
         <v>7340</v>
       </c>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C29" s="4" t="s">
         <v>38</v>
       </c>
@@ -6076,7 +6132,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C30" s="4" t="s">
         <v>39</v>
       </c>
@@ -6097,7 +6153,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C31" s="4" t="s">
         <v>40</v>
       </c>
@@ -6118,7 +6174,7 @@
         <v>2786</v>
       </c>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C32" s="4" t="s">
         <v>41</v>
       </c>
@@ -6139,7 +6195,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="33" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C33" s="4" t="s">
         <v>42</v>
       </c>
@@ -6160,7 +6216,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="34" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C34" s="4" t="s">
         <v>43</v>
       </c>
@@ -6181,7 +6237,7 @@
         <v>3105</v>
       </c>
     </row>
-    <row r="35" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C35" s="4" t="s">
         <v>44</v>
       </c>
@@ -6202,7 +6258,7 @@
         <v>3479</v>
       </c>
     </row>
-    <row r="36" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C36" s="4" t="s">
         <v>45</v>
       </c>
@@ -6223,7 +6279,7 @@
         <v>9727</v>
       </c>
     </row>
-    <row r="37" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C37" s="4" t="s">
         <v>46</v>
       </c>
@@ -6244,7 +6300,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="38" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C38" s="4" t="s">
         <v>47</v>
       </c>
@@ -6265,7 +6321,7 @@
         <v>8407</v>
       </c>
     </row>
-    <row r="39" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>48</v>
       </c>
@@ -6286,7 +6342,7 @@
         <v>4832</v>
       </c>
     </row>
-    <row r="40" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>49</v>
       </c>
@@ -6307,7 +6363,7 @@
         <v>8286</v>
       </c>
     </row>
-    <row r="41" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C41" s="4" t="s">
         <v>50</v>
       </c>
@@ -6328,7 +6384,7 @@
         <v>6691</v>
       </c>
     </row>
-    <row r="42" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C42" s="4" t="s">
         <v>51</v>
       </c>
@@ -6349,7 +6405,7 @@
         <v>8077</v>
       </c>
     </row>
-    <row r="43" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C43" s="4" t="s">
         <v>52</v>
       </c>
@@ -6370,7 +6426,7 @@
         <v>5800</v>
       </c>
     </row>
-    <row r="44" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C44" s="4" t="s">
         <v>53</v>
       </c>
@@ -6391,7 +6447,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="45" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C45" s="4" t="s">
         <v>54</v>
       </c>
@@ -6412,7 +6468,7 @@
         <v>8022</v>
       </c>
     </row>
-    <row r="46" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C46" s="4" t="s">
         <v>55</v>
       </c>
@@ -6433,7 +6489,7 @@
         <v>7087</v>
       </c>
     </row>
-    <row r="47" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C47" s="4" t="s">
         <v>56</v>
       </c>
@@ -6454,7 +6510,7 @@
         <v>9331</v>
       </c>
     </row>
-    <row r="48" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C48" s="4" t="s">
         <v>57</v>
       </c>
@@ -6475,7 +6531,7 @@
         <v>10794</v>
       </c>
     </row>
-    <row r="49" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C49" s="4" t="s">
         <v>58</v>
       </c>
@@ -6496,7 +6552,7 @@
         <v>3721</v>
       </c>
     </row>
-    <row r="50" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C50" s="4" t="s">
         <v>59</v>
       </c>
@@ -6517,7 +6573,7 @@
         <v>10706</v>
       </c>
     </row>
-    <row r="51" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C51" s="4" t="s">
         <v>60</v>
       </c>
@@ -6538,7 +6594,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="52" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C52" s="4" t="s">
         <v>61</v>
       </c>
@@ -6559,7 +6615,7 @@
         <v>2511</v>
       </c>
     </row>
-    <row r="53" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C53" s="4" t="s">
         <v>62</v>
       </c>
@@ -6580,7 +6636,7 @@
         <v>2995</v>
       </c>
     </row>
-    <row r="54" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C54" s="4" t="s">
         <v>63</v>
       </c>
@@ -6601,7 +6657,7 @@
         <v>3567</v>
       </c>
     </row>
-    <row r="55" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C55" s="4" t="s">
         <v>64</v>
       </c>
@@ -6622,7 +6678,7 @@
         <v>4227</v>
       </c>
     </row>
-    <row r="56" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C56" s="4" t="s">
         <v>65</v>
       </c>
@@ -6643,7 +6699,7 @@
         <v>3248</v>
       </c>
     </row>
-    <row r="57" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C57" s="4" t="s">
         <v>66</v>
       </c>
@@ -6664,7 +6720,7 @@
         <v>3655</v>
       </c>
     </row>
-    <row r="58" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C58" s="4" t="s">
         <v>67</v>
       </c>
@@ -6685,7 +6741,7 @@
         <v>10002</v>
       </c>
     </row>
-    <row r="59" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C59" s="4" t="s">
         <v>68</v>
       </c>
@@ -6706,7 +6762,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="60" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C60" s="4" t="s">
         <v>69</v>
       </c>
@@ -6727,7 +6783,7 @@
         <v>6537</v>
       </c>
     </row>
-    <row r="61" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C61" s="4" t="s">
         <v>70</v>
       </c>
@@ -6748,7 +6804,7 @@
         <v>4326</v>
       </c>
     </row>
-    <row r="62" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C62" s="4" t="s">
         <v>71</v>
       </c>
@@ -6769,7 +6825,7 @@
         <v>4491</v>
       </c>
     </row>
-    <row r="63" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C63" s="4" t="s">
         <v>72</v>
       </c>
@@ -6790,7 +6846,7 @@
         <v>2335</v>
       </c>
     </row>
-    <row r="64" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C64" s="4" t="s">
         <v>73</v>
       </c>
@@ -6811,7 +6867,7 @@
         <v>10376</v>
       </c>
     </row>
-    <row r="65" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C65" s="4" t="s">
         <v>74</v>
       </c>
@@ -6832,7 +6888,7 @@
         <v>8649</v>
       </c>
     </row>
-    <row r="66" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C66" s="4" t="s">
         <v>75</v>
       </c>
@@ -6853,7 +6909,7 @@
         <v>9870</v>
       </c>
     </row>
-    <row r="67" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C67" s="4" t="s">
         <v>76</v>
       </c>
@@ -6874,7 +6930,7 @@
         <v>10134</v>
       </c>
     </row>
-    <row r="68" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C68" s="4" t="s">
         <v>77</v>
       </c>
@@ -6895,7 +6951,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="69" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C69" s="4" t="s">
         <v>78</v>
       </c>
@@ -6916,7 +6972,7 @@
         <v>7846</v>
       </c>
     </row>
-    <row r="70" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C70" s="4" t="s">
         <v>79</v>
       </c>
@@ -6937,7 +6993,7 @@
         <v>4612</v>
       </c>
     </row>
-    <row r="71" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C71" s="4" t="s">
         <v>80</v>
       </c>
@@ -6958,7 +7014,7 @@
         <v>9650</v>
       </c>
     </row>
-    <row r="72" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C72" s="4" t="s">
         <v>81</v>
       </c>
@@ -6979,7 +7035,7 @@
         <v>8341</v>
       </c>
     </row>
-    <row r="73" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C73" s="4" t="s">
         <v>82</v>
       </c>
@@ -7000,7 +7056,7 @@
         <v>7384</v>
       </c>
     </row>
-    <row r="74" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C74" s="4" t="s">
         <v>83</v>
       </c>
@@ -7021,7 +7077,7 @@
         <v>9067</v>
       </c>
     </row>
-    <row r="75" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C75" s="4" t="s">
         <v>84</v>
       </c>
@@ -7042,7 +7098,7 @@
         <v>6988</v>
       </c>
     </row>
-    <row r="76" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C76" s="4" t="s">
         <v>85</v>
       </c>
@@ -7063,7 +7119,7 @@
         <v>4491</v>
       </c>
     </row>
-    <row r="77" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C77" s="4" t="s">
         <v>86</v>
       </c>
@@ -7084,7 +7140,7 @@
         <v>10167</v>
       </c>
     </row>
-    <row r="78" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C78" s="4" t="s">
         <v>87</v>
       </c>
@@ -7105,7 +7161,7 @@
         <v>2599</v>
       </c>
     </row>
-    <row r="79" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C79" s="4" t="s">
         <v>88</v>
       </c>
@@ -7126,7 +7182,7 @@
         <v>3468</v>
       </c>
     </row>
-    <row r="80" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C80" s="4" t="s">
         <v>89</v>
       </c>
@@ -7147,7 +7203,7 @@
         <v>10035</v>
       </c>
     </row>
-    <row r="81" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C81" s="4" t="s">
         <v>90</v>
       </c>
@@ -7168,7 +7224,7 @@
         <v>3017</v>
       </c>
     </row>
-    <row r="82" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C82" s="4" t="s">
         <v>91</v>
       </c>
@@ -7189,7 +7245,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="83" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C83" s="4" t="s">
         <v>92</v>
       </c>
@@ -7210,7 +7266,7 @@
         <v>7626</v>
       </c>
     </row>
-    <row r="84" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C84" s="4" t="s">
         <v>93</v>
       </c>
@@ -7231,7 +7287,7 @@
         <v>4733</v>
       </c>
     </row>
-    <row r="85" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C85" s="4" t="s">
         <v>94</v>
       </c>
@@ -7252,7 +7308,7 @@
         <v>9936</v>
       </c>
     </row>
-    <row r="86" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C86" s="4" t="s">
         <v>95</v>
       </c>
@@ -7273,7 +7329,7 @@
         <v>3127</v>
       </c>
     </row>
-    <row r="87" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C87" s="4" t="s">
         <v>96</v>
       </c>
@@ -7294,7 +7350,7 @@
         <v>7461</v>
       </c>
     </row>
-    <row r="88" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C88" s="4" t="s">
         <v>97</v>
       </c>
@@ -7315,7 +7371,7 @@
         <v>3490</v>
       </c>
     </row>
-    <row r="89" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C89" s="4" t="s">
         <v>98</v>
       </c>
@@ -7336,7 +7392,7 @@
         <v>3369</v>
       </c>
     </row>
-    <row r="90" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C90" s="4" t="s">
         <v>99</v>
       </c>
@@ -7357,7 +7413,7 @@
         <v>10684</v>
       </c>
     </row>
-    <row r="91" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C91" s="4" t="s">
         <v>100</v>
       </c>
@@ -7378,7 +7434,7 @@
         <v>3996</v>
       </c>
     </row>
-    <row r="92" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C92" s="4" t="s">
         <v>101</v>
       </c>
@@ -7399,7 +7455,7 @@
         <v>9210</v>
       </c>
     </row>
-    <row r="93" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C93" s="4" t="s">
         <v>102</v>
       </c>
@@ -7420,7 +7476,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="94" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C94" s="4" t="s">
         <v>103</v>
       </c>
@@ -7441,7 +7497,7 @@
         <v>6504</v>
       </c>
     </row>
-    <row r="95" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C95" s="4" t="s">
         <v>104</v>
       </c>
@@ -7462,7 +7518,7 @@
         <v>9386</v>
       </c>
     </row>
-    <row r="96" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C96" s="4" t="s">
         <v>105</v>
       </c>
@@ -7483,7 +7539,7 @@
         <v>10607</v>
       </c>
     </row>
-    <row r="97" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C97" s="4" t="s">
         <v>106</v>
       </c>
@@ -7504,7 +7560,7 @@
         <v>8836</v>
       </c>
     </row>
-    <row r="98" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C98" s="4" t="s">
         <v>107</v>
       </c>
@@ -7525,7 +7581,7 @@
         <v>7560</v>
       </c>
     </row>
-    <row r="99" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C99" s="4" t="s">
         <v>108</v>
       </c>
@@ -7546,7 +7602,7 @@
         <v>2830</v>
       </c>
     </row>
-    <row r="100" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C100" s="4" t="s">
         <v>109</v>
       </c>
@@ -7567,7 +7623,7 @@
         <v>2654</v>
       </c>
     </row>
-    <row r="101" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C101" s="4" t="s">
         <v>110</v>
       </c>
@@ -7588,7 +7644,7 @@
         <v>6933</v>
       </c>
     </row>
-    <row r="102" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -7604,13 +7660,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V120"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>211</v>
       </c>
@@ -7645,7 +7701,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -7708,7 +7764,7 @@
         <v>2337.4802333478292</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -7771,7 +7827,7 @@
         <v>8600.3320817389467</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -7834,7 +7890,7 @@
         <v>3087.6837878067308</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
@@ -7891,7 +7947,7 @@
         <v>9782.3977311280323</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
         <v>15</v>
       </c>
@@ -7948,7 +8004,7 @@
         <v>3481.8136465466232</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
@@ -8005,7 +8061,7 @@
         <v>8602.2540668699949</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
@@ -8062,7 +8118,7 @@
         <v>10938.776406861609</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C9" s="4" t="s">
         <v>18</v>
       </c>
@@ -8119,7 +8175,7 @@
         <v>3589.8628493610886</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C10" s="4" t="s">
         <v>19</v>
       </c>
@@ -8176,7 +8232,7 @@
         <v>9983.0849128052068</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C11" s="4" t="s">
         <v>20</v>
       </c>
@@ -8233,7 +8289,7 @@
         <v>8701.3569174471777</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
         <v>21</v>
       </c>
@@ -8290,7 +8346,7 @@
         <v>1409.8717172527686</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C13" s="4" t="s">
         <v>22</v>
       </c>
@@ -8347,7 +8403,7 @@
         <v>7548.730412127974</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C14" s="4" t="s">
         <v>23</v>
       </c>
@@ -8404,7 +8460,7 @@
         <v>3531.0737826515688</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C15" s="4" t="s">
         <v>24</v>
       </c>
@@ -8461,7 +8517,7 @@
         <v>7262.7373080027173</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C16" s="4" t="s">
         <v>25</v>
       </c>
@@ -8518,7 +8574,7 @@
         <v>4808.8002030476928</v>
       </c>
     </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C17" s="4" t="s">
         <v>26</v>
       </c>
@@ -8575,7 +8631,7 @@
         <v>7558.8675631357182</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C18" s="4" t="s">
         <v>27</v>
       </c>
@@ -8632,7 +8688,7 @@
         <v>8784.7713039091614</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C19" s="4" t="s">
         <v>28</v>
       </c>
@@ -8689,7 +8745,7 @@
         <v>5111.8047585601453</v>
       </c>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C20" s="4" t="s">
         <v>29</v>
       </c>
@@ -8746,7 +8802,7 @@
         <v>5682.2765748023521</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C21" s="4" t="s">
         <v>30</v>
       </c>
@@ -8803,7 +8859,7 @@
         <v>7984.8433041633398</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C22" s="4" t="s">
         <v>31</v>
       </c>
@@ -8860,7 +8916,7 @@
         <v>697.9992561697436</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C23" s="4" t="s">
         <v>32</v>
       </c>
@@ -8917,7 +8973,7 @@
         <v>3302.848957572307</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C24" s="4" t="s">
         <v>33</v>
       </c>
@@ -8974,7 +9030,7 @@
         <v>7580.2399848754867</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C25" s="4" t="s">
         <v>34</v>
       </c>
@@ -9031,7 +9087,7 @@
         <v>3083.1541521619074</v>
       </c>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C26" s="4" t="s">
         <v>35</v>
       </c>
@@ -9088,7 +9144,7 @@
         <v>7718.5856544652779</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C27" s="4" t="s">
         <v>36</v>
       </c>
@@ -9145,7 +9201,7 @@
         <v>2421.9722755344701</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C28" s="4" t="s">
         <v>37</v>
       </c>
@@ -9202,7 +9258,7 @@
         <v>7344.4274702304392</v>
       </c>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C29" s="4" t="s">
         <v>38</v>
       </c>
@@ -9259,7 +9315,7 @@
         <v>1037.7126046461635</v>
       </c>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C30" s="4" t="s">
         <v>39</v>
       </c>
@@ -9316,7 +9372,7 @@
         <v>2759.3921326323325</v>
       </c>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C31" s="4" t="s">
         <v>40</v>
       </c>
@@ -9373,7 +9429,7 @@
         <v>2773.1280078878044</v>
       </c>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C32" s="4" t="s">
         <v>41</v>
       </c>
@@ -9430,7 +9486,7 @@
         <v>1199.6305987830274</v>
       </c>
     </row>
-    <row r="33" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C33" s="4" t="s">
         <v>42</v>
       </c>
@@ -9487,7 +9543,7 @@
         <v>2048.7896543391107</v>
       </c>
     </row>
-    <row r="34" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C34" s="4" t="s">
         <v>43</v>
       </c>
@@ -9544,7 +9600,7 @@
         <v>3110.5411624089174</v>
       </c>
     </row>
-    <row r="35" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C35" s="4" t="s">
         <v>44</v>
       </c>
@@ -9601,7 +9657,7 @@
         <v>3489.6633115137811</v>
       </c>
     </row>
-    <row r="36" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C36" s="4" t="s">
         <v>45</v>
       </c>
@@ -9658,7 +9714,7 @@
         <v>9724.2359057665017</v>
       </c>
     </row>
-    <row r="37" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C37" s="4" t="s">
         <v>46</v>
       </c>
@@ -9715,7 +9771,7 @@
         <v>847.87112719283323</v>
       </c>
     </row>
-    <row r="38" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C38" s="4" t="s">
         <v>47</v>
       </c>
@@ -9772,7 +9828,7 @@
         <v>8411.8107744987647</v>
       </c>
     </row>
-    <row r="39" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>48</v>
       </c>
@@ -9829,7 +9885,7 @@
         <v>4834.3668235371588</v>
       </c>
     </row>
-    <row r="40" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>49</v>
       </c>
@@ -9886,7 +9942,7 @@
         <v>8279.953119883372</v>
       </c>
     </row>
-    <row r="41" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C41" s="4" t="s">
         <v>50</v>
       </c>
@@ -9943,7 +9999,7 @@
         <v>6684.8743758320925</v>
       </c>
     </row>
-    <row r="42" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C42" s="4" t="s">
         <v>51</v>
       </c>
@@ -10000,7 +10056,7 @@
         <v>8100.0305886361748</v>
       </c>
     </row>
-    <row r="43" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C43" s="4" t="s">
         <v>52</v>
       </c>
@@ -10057,7 +10113,7 @@
         <v>5797.1838974488492</v>
       </c>
     </row>
-    <row r="44" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C44" s="4" t="s">
         <v>53</v>
       </c>
@@ -10114,7 +10170,7 @@
         <v>2980.5377173793968</v>
       </c>
     </row>
-    <row r="45" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C45" s="4" t="s">
         <v>54</v>
       </c>
@@ -10171,7 +10227,7 @@
         <v>8024.4310281787621</v>
       </c>
     </row>
-    <row r="46" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C46" s="4" t="s">
         <v>55</v>
       </c>
@@ -10228,7 +10284,7 @@
         <v>7079.479820321023</v>
       </c>
     </row>
-    <row r="47" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C47" s="4" t="s">
         <v>56</v>
       </c>
@@ -10285,7 +10341,7 @@
         <v>9321.8192171460541</v>
       </c>
     </row>
-    <row r="48" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C48" s="4" t="s">
         <v>57</v>
       </c>
@@ -10342,7 +10398,7 @@
         <v>10782.208242029941</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C49" s="4" t="s">
         <v>58</v>
       </c>
@@ -10399,7 +10455,7 @@
         <v>3717.4016444664594</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C50" s="4" t="s">
         <v>59</v>
       </c>
@@ -10456,7 +10512,7 @@
         <v>10705.4899030753</v>
       </c>
     </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C51" s="4" t="s">
         <v>60</v>
       </c>
@@ -10513,7 +10569,7 @@
         <v>1931.0214755497582</v>
       </c>
     </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C52" s="4" t="s">
         <v>61</v>
       </c>
@@ -10570,7 +10626,7 @@
         <v>2509.2285044097807</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C53" s="4" t="s">
         <v>62</v>
       </c>
@@ -10627,7 +10683,7 @@
         <v>2990.250813890365</v>
       </c>
     </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C54" s="4" t="s">
         <v>63</v>
       </c>
@@ -10684,7 +10740,7 @@
         <v>3561.9597054182959</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C55" s="4" t="s">
         <v>64</v>
       </c>
@@ -10741,7 +10797,7 @@
         <v>4215.8665979597135</v>
       </c>
     </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C56" s="4" t="s">
         <v>65</v>
       </c>
@@ -10798,7 +10854,7 @@
         <v>3257.3032576842234</v>
       </c>
     </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="4" t="s">
         <v>66</v>
       </c>
@@ -10855,7 +10911,7 @@
         <v>3654.3098026607186</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C58" s="4" t="s">
         <v>67</v>
       </c>
@@ -10912,7 +10968,7 @@
         <v>9995.2062382868025</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C59" s="4" t="s">
         <v>68</v>
       </c>
@@ -10969,7 +11025,7 @@
         <v>1677.2776229393785</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C60" s="4" t="s">
         <v>69</v>
       </c>
@@ -11026,7 +11082,7 @@
         <v>6531.1767188374652</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C61" s="4" t="s">
         <v>70</v>
       </c>
@@ -11083,7 +11139,7 @@
         <v>4333.0763439907751</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C62" s="4" t="s">
         <v>71</v>
       </c>
@@ -11140,7 +11196,7 @@
         <v>4488.9531764893181</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C63" s="4" t="s">
         <v>72</v>
       </c>
@@ -11197,7 +11253,7 @@
         <v>2337.1345306322473</v>
       </c>
     </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C64" s="4" t="s">
         <v>73</v>
       </c>
@@ -11254,7 +11310,7 @@
         <v>10381.069312010164</v>
       </c>
     </row>
-    <row r="65" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C65" s="4" t="s">
         <v>74</v>
       </c>
@@ -11311,7 +11367,7 @@
         <v>8643.6842854114948</v>
       </c>
     </row>
-    <row r="66" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C66" s="4" t="s">
         <v>75</v>
       </c>
@@ -11368,7 +11424,7 @@
         <v>9870.2578724433988</v>
       </c>
     </row>
-    <row r="67" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C67" s="4" t="s">
         <v>76</v>
       </c>
@@ -11425,7 +11481,7 @@
         <v>10132.788399580008</v>
       </c>
     </row>
-    <row r="68" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C68" s="4" t="s">
         <v>77</v>
       </c>
@@ -11482,7 +11538,7 @@
         <v>1650.1798244486563</v>
       </c>
     </row>
-    <row r="69" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C69" s="4" t="s">
         <v>78</v>
       </c>
@@ -11539,7 +11595,7 @@
         <v>7842.7130630920874</v>
       </c>
     </row>
-    <row r="70" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C70" s="4" t="s">
         <v>79</v>
       </c>
@@ -11596,7 +11652,7 @@
         <v>4624.5273027151707</v>
       </c>
     </row>
-    <row r="71" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C71" s="4" t="s">
         <v>80</v>
       </c>
@@ -11653,7 +11709,7 @@
         <v>9653.7217512272036</v>
       </c>
     </row>
-    <row r="72" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C72" s="4" t="s">
         <v>81</v>
       </c>
@@ -11710,7 +11766,7 @@
         <v>8334.8091173135035</v>
       </c>
     </row>
-    <row r="73" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C73" s="4" t="s">
         <v>82</v>
       </c>
@@ -11767,7 +11823,7 @@
         <v>7401.1249484992586</v>
       </c>
     </row>
-    <row r="74" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C74" s="4" t="s">
         <v>83</v>
       </c>
@@ -11824,7 +11880,7 @@
         <v>9063.9719280215795</v>
       </c>
     </row>
-    <row r="75" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C75" s="4" t="s">
         <v>84</v>
       </c>
@@ -11881,7 +11937,7 @@
         <v>6986.3685708229896</v>
       </c>
     </row>
-    <row r="76" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C76" s="4" t="s">
         <v>85</v>
       </c>
@@ -11938,7 +11994,7 @@
         <v>4492.1858980997204</v>
       </c>
     </row>
-    <row r="77" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C77" s="4" t="s">
         <v>86</v>
       </c>
@@ -11995,7 +12051,7 @@
         <v>10158.488848536392</v>
       </c>
     </row>
-    <row r="78" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C78" s="4" t="s">
         <v>87</v>
       </c>
@@ -12052,7 +12108,7 @@
         <v>2601.9487273423001</v>
       </c>
     </row>
-    <row r="79" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C79" s="4" t="s">
         <v>88</v>
       </c>
@@ -12109,7 +12165,7 @@
         <v>3469.822756985348</v>
       </c>
     </row>
-    <row r="80" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C80" s="4" t="s">
         <v>89</v>
       </c>
@@ -12166,7 +12222,7 @@
         <v>10034.138419752853</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C81" s="4" t="s">
         <v>90</v>
       </c>
@@ -12223,7 +12279,7 @@
         <v>3013.8979039294645</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C82" s="4" t="s">
         <v>91</v>
       </c>
@@ -12280,7 +12336,7 @@
         <v>4443.1984437049832</v>
       </c>
     </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C83" s="4" t="s">
         <v>92</v>
       </c>
@@ -12337,7 +12393,7 @@
         <v>7623.130344127072</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C84" s="4" t="s">
         <v>93</v>
       </c>
@@ -12394,7 +12450,7 @@
         <v>4734.7265881524509</v>
       </c>
     </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C85" s="4" t="s">
         <v>94</v>
       </c>
@@ -12451,7 +12507,7 @@
         <v>9933.7377865434391</v>
       </c>
     </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C86" s="4" t="s">
         <v>95</v>
       </c>
@@ -12508,7 +12564,7 @@
         <v>3125.8995744388085</v>
       </c>
     </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C87" s="4" t="s">
         <v>96</v>
       </c>
@@ -12565,7 +12621,7 @@
         <v>7455.5955141811282</v>
       </c>
     </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C88" s="4" t="s">
         <v>97</v>
       </c>
@@ -12622,7 +12678,7 @@
         <v>3491.2741577393172</v>
       </c>
     </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C89" s="4" t="s">
         <v>98</v>
       </c>
@@ -12679,7 +12735,7 @@
         <v>3382.7469760375097</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C90" s="4" t="s">
         <v>99</v>
       </c>
@@ -12736,7 +12792,7 @@
         <v>10682.871021489322</v>
       </c>
     </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C91" s="4" t="s">
         <v>100</v>
       </c>
@@ -12793,7 +12849,7 @@
         <v>3994.640948888351</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C92" s="4" t="s">
         <v>101</v>
       </c>
@@ -12850,7 +12906,7 @@
         <v>9221.4680642582243</v>
       </c>
     </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C93" s="4" t="s">
         <v>102</v>
       </c>
@@ -12907,7 +12963,7 @@
         <v>744.21346157963853</v>
       </c>
     </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C94" s="4" t="s">
         <v>103</v>
       </c>
@@ -12964,7 +13020,7 @@
         <v>6496.6109236639459</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C95" s="4" t="s">
         <v>104</v>
       </c>
@@ -13021,7 +13077,7 @@
         <v>9395.806437901716</v>
       </c>
     </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C96" s="4" t="s">
         <v>105</v>
       </c>
@@ -13078,7 +13134,7 @@
         <v>10600.949681993399</v>
       </c>
     </row>
-    <row r="97" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C97" s="4" t="s">
         <v>106</v>
       </c>
@@ -13135,7 +13191,7 @@
         <v>8832.3314235174039</v>
       </c>
     </row>
-    <row r="98" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C98" s="4" t="s">
         <v>107</v>
       </c>
@@ -13192,7 +13248,7 @@
         <v>7551.7511718194874</v>
       </c>
     </row>
-    <row r="99" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C99" s="4" t="s">
         <v>108</v>
       </c>
@@ -13249,7 +13305,7 @@
         <v>2821.9513879831356</v>
       </c>
     </row>
-    <row r="100" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C100" s="4" t="s">
         <v>109</v>
       </c>
@@ -13306,7 +13362,7 @@
         <v>2655.1289785106783</v>
       </c>
     </row>
-    <row r="101" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C101" s="4" t="s">
         <v>110</v>
       </c>
@@ -13363,7 +13419,7 @@
         <v>6935.9044243079998</v>
       </c>
     </row>
-    <row r="103" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C103" s="8" t="s">
         <v>339</v>
       </c>
@@ -13405,7 +13461,7 @@
       </c>
       <c r="V103" s="9"/>
     </row>
-    <row r="104" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C104" s="10" cm="1">
         <f t="array" ref="C104:D108">LINEST(H2:H101,$E$2:$E$101,1,1)</f>
         <v>11.002207636744096</v>
@@ -13477,7 +13533,7 @@
         <v>14.527435737875749</v>
       </c>
     </row>
-    <row r="105" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C105" s="10">
         <v>2.8746203710838789E-3</v>
       </c>
@@ -13539,7 +13595,7 @@
         <v>1.6866505513277985</v>
       </c>
     </row>
-    <row r="106" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C106" s="10">
         <v>0.99999331002500658</v>
       </c>
@@ -13601,7 +13657,7 @@
         <v>7.7491532903948492</v>
       </c>
     </row>
-    <row r="107" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C107" s="10">
         <v>14648686.20266065</v>
       </c>
@@ -13663,7 +13719,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="108" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C108" s="12">
         <v>916700720.17655551</v>
       </c>
@@ -13725,7 +13781,7 @@
         <v>5884.8389183676572</v>
       </c>
     </row>
-    <row r="110" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C110" t="s">
         <v>351</v>
       </c>
@@ -13733,7 +13789,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="111" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C111" s="4"/>
       <c r="F111" t="s">
         <v>354</v>
@@ -13745,7 +13801,7 @@
       <c r="L111" s="4"/>
       <c r="O111" s="4"/>
     </row>
-    <row r="112" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B112" s="14"/>
       <c r="C112" s="15" t="s">
         <v>354</v>
@@ -13763,7 +13819,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="10" t="s">
         <v>357</v>
       </c>
@@ -13780,7 +13836,7 @@
         <v>8.5798335111756572</v>
       </c>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="10" t="s">
         <v>352</v>
       </c>
@@ -13797,7 +13853,7 @@
         <v>7.7491532903948492</v>
       </c>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="10" t="s">
         <v>353</v>
       </c>
@@ -13814,7 +13870,7 @@
         <v>9.6989610537075688</v>
       </c>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="12" t="s">
         <v>356</v>
       </c>
@@ -13831,7 +13887,7 @@
         <v>1.9498077633127195</v>
       </c>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C118" s="18" t="s">
         <v>361</v>
       </c>
@@ -13843,7 +13899,7 @@
       <c r="I118" s="18"/>
       <c r="J118" s="18"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C119" s="18"/>
       <c r="D119" s="18"/>
       <c r="E119" s="18"/>
@@ -13853,7 +13909,7 @@
       <c r="I119" s="18"/>
       <c r="J119" s="18"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C120" s="18"/>
       <c r="D120" s="18"/>
       <c r="E120" s="18"/>
@@ -13875,12 +13931,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:V122"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>212</v>
       </c>
@@ -13891,7 +13947,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="H2" t="s">
         <v>329</v>
@@ -13924,7 +13980,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -13987,7 +14043,7 @@
         <v>2437.4802333478292</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -14050,7 +14106,7 @@
         <v>8700.3320817389467</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -14113,7 +14169,7 @@
         <v>3187.6837878067308</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
@@ -14170,7 +14226,7 @@
         <v>9882.3977311280323</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
@@ -14227,7 +14283,7 @@
         <v>3581.8136465466232</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C8" s="4" t="s">
         <v>16</v>
       </c>
@@ -14284,7 +14340,7 @@
         <v>8702.2540668699949</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C9" s="4" t="s">
         <v>17</v>
       </c>
@@ -14341,7 +14397,7 @@
         <v>11038.776406861609</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C10" s="4" t="s">
         <v>18</v>
       </c>
@@ -14398,7 +14454,7 @@
         <v>3689.8628493610886</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C11" s="4" t="s">
         <v>19</v>
       </c>
@@ -14455,7 +14511,7 @@
         <v>10083.084912805207</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
         <v>20</v>
       </c>
@@ -14512,7 +14568,7 @@
         <v>8801.3569174471777</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C13" s="4" t="s">
         <v>21</v>
       </c>
@@ -14569,7 +14625,7 @@
         <v>1509.8717172527686</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
@@ -14626,7 +14682,7 @@
         <v>7648.730412127974</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C15" s="4" t="s">
         <v>23</v>
       </c>
@@ -14683,7 +14739,7 @@
         <v>3631.0737826515688</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C16" s="4" t="s">
         <v>24</v>
       </c>
@@ -14740,7 +14796,7 @@
         <v>7362.7373080027173</v>
       </c>
     </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C17" s="4" t="s">
         <v>25</v>
       </c>
@@ -14797,7 +14853,7 @@
         <v>4908.8002030476928</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C18" s="4" t="s">
         <v>26</v>
       </c>
@@ -14854,7 +14910,7 @@
         <v>7658.8675631357182</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C19" s="4" t="s">
         <v>27</v>
       </c>
@@ -14911,7 +14967,7 @@
         <v>8884.7713039091614</v>
       </c>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C20" s="4" t="s">
         <v>28</v>
       </c>
@@ -14968,7 +15024,7 @@
         <v>5211.8047585601453</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C21" s="4" t="s">
         <v>29</v>
       </c>
@@ -15025,7 +15081,7 @@
         <v>5782.2765748023521</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C22" s="4" t="s">
         <v>30</v>
       </c>
@@ -15082,7 +15138,7 @@
         <v>8084.8433041633398</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C23" s="4" t="s">
         <v>31</v>
       </c>
@@ -15139,7 +15195,7 @@
         <v>797.9992561697436</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C24" s="4" t="s">
         <v>32</v>
       </c>
@@ -15196,7 +15252,7 @@
         <v>3402.848957572307</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C25" s="4" t="s">
         <v>33</v>
       </c>
@@ -15253,7 +15309,7 @@
         <v>7680.2399848754867</v>
       </c>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C26" s="4" t="s">
         <v>34</v>
       </c>
@@ -15310,7 +15366,7 @@
         <v>3183.1541521619074</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C27" s="4" t="s">
         <v>35</v>
       </c>
@@ -15367,7 +15423,7 @@
         <v>7818.5856544652779</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C28" s="4" t="s">
         <v>36</v>
       </c>
@@ -15424,7 +15480,7 @@
         <v>2521.9722755344701</v>
       </c>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C29" s="4" t="s">
         <v>37</v>
       </c>
@@ -15481,7 +15537,7 @@
         <v>7444.4274702304392</v>
       </c>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C30" s="4" t="s">
         <v>38</v>
       </c>
@@ -15538,7 +15594,7 @@
         <v>1137.7126046461635</v>
       </c>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C31" s="4" t="s">
         <v>39</v>
       </c>
@@ -15595,7 +15651,7 @@
         <v>2859.3921326323325</v>
       </c>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C32" s="4" t="s">
         <v>40</v>
       </c>
@@ -15652,7 +15708,7 @@
         <v>2873.1280078878044</v>
       </c>
     </row>
-    <row r="33" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C33" s="4" t="s">
         <v>41</v>
       </c>
@@ -15709,7 +15765,7 @@
         <v>1299.6305987830274</v>
       </c>
     </row>
-    <row r="34" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C34" s="4" t="s">
         <v>42</v>
       </c>
@@ -15766,7 +15822,7 @@
         <v>2148.7896543391107</v>
       </c>
     </row>
-    <row r="35" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C35" s="4" t="s">
         <v>43</v>
       </c>
@@ -15823,7 +15879,7 @@
         <v>3210.5411624089174</v>
       </c>
     </row>
-    <row r="36" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C36" s="4" t="s">
         <v>44</v>
       </c>
@@ -15880,7 +15936,7 @@
         <v>3589.6633115137811</v>
       </c>
     </row>
-    <row r="37" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C37" s="4" t="s">
         <v>45</v>
       </c>
@@ -15937,7 +15993,7 @@
         <v>9824.2359057665017</v>
       </c>
     </row>
-    <row r="38" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C38" s="4" t="s">
         <v>46</v>
       </c>
@@ -15994,7 +16050,7 @@
         <v>947.87112719283323</v>
       </c>
     </row>
-    <row r="39" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>47</v>
       </c>
@@ -16051,7 +16107,7 @@
         <v>8511.8107744987647</v>
       </c>
     </row>
-    <row r="40" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>48</v>
       </c>
@@ -16108,7 +16164,7 @@
         <v>4934.3668235371588</v>
       </c>
     </row>
-    <row r="41" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C41" s="4" t="s">
         <v>49</v>
       </c>
@@ -16165,7 +16221,7 @@
         <v>8379.953119883372</v>
       </c>
     </row>
-    <row r="42" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C42" s="4" t="s">
         <v>50</v>
       </c>
@@ -16222,7 +16278,7 @@
         <v>6784.8743758320925</v>
       </c>
     </row>
-    <row r="43" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C43" s="4" t="s">
         <v>51</v>
       </c>
@@ -16279,7 +16335,7 @@
         <v>8200.0305886361748</v>
       </c>
     </row>
-    <row r="44" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C44" s="4" t="s">
         <v>52</v>
       </c>
@@ -16336,7 +16392,7 @@
         <v>5897.1838974488492</v>
       </c>
     </row>
-    <row r="45" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C45" s="4" t="s">
         <v>53</v>
       </c>
@@ -16393,7 +16449,7 @@
         <v>3080.5377173793968</v>
       </c>
     </row>
-    <row r="46" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C46" s="4" t="s">
         <v>54</v>
       </c>
@@ -16450,7 +16506,7 @@
         <v>8124.4310281787621</v>
       </c>
     </row>
-    <row r="47" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C47" s="4" t="s">
         <v>55</v>
       </c>
@@ -16507,7 +16563,7 @@
         <v>7179.479820321023</v>
       </c>
     </row>
-    <row r="48" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C48" s="4" t="s">
         <v>56</v>
       </c>
@@ -16564,7 +16620,7 @@
         <v>9421.8192171460541</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C49" s="4" t="s">
         <v>57</v>
       </c>
@@ -16621,7 +16677,7 @@
         <v>10882.208242029941</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C50" s="4" t="s">
         <v>58</v>
       </c>
@@ -16678,7 +16734,7 @@
         <v>3817.4016444664594</v>
       </c>
     </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C51" s="4" t="s">
         <v>59</v>
       </c>
@@ -16735,7 +16791,7 @@
         <v>10805.4899030753</v>
       </c>
     </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C52" s="4" t="s">
         <v>60</v>
       </c>
@@ -16792,7 +16848,7 @@
         <v>2031.0214755497582</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C53" s="4" t="s">
         <v>61</v>
       </c>
@@ -16849,7 +16905,7 @@
         <v>2609.2285044097807</v>
       </c>
     </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C54" s="4" t="s">
         <v>62</v>
       </c>
@@ -16906,7 +16962,7 @@
         <v>3090.250813890365</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C55" s="4" t="s">
         <v>63</v>
       </c>
@@ -16963,7 +17019,7 @@
         <v>3661.9597054182959</v>
       </c>
     </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C56" s="4" t="s">
         <v>64</v>
       </c>
@@ -17020,7 +17076,7 @@
         <v>4315.8665979597135</v>
       </c>
     </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="4" t="s">
         <v>65</v>
       </c>
@@ -17077,7 +17133,7 @@
         <v>3357.3032576842234</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C58" s="4" t="s">
         <v>66</v>
       </c>
@@ -17134,7 +17190,7 @@
         <v>3754.3098026607186</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C59" s="4" t="s">
         <v>67</v>
       </c>
@@ -17191,7 +17247,7 @@
         <v>10095.206238286803</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C60" s="4" t="s">
         <v>68</v>
       </c>
@@ -17248,7 +17304,7 @@
         <v>1777.2776229393785</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C61" s="4" t="s">
         <v>69</v>
       </c>
@@ -17305,7 +17361,7 @@
         <v>6631.1767188374652</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C62" s="4" t="s">
         <v>70</v>
       </c>
@@ -17362,7 +17418,7 @@
         <v>4433.0763439907751</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C63" s="4" t="s">
         <v>71</v>
       </c>
@@ -17419,7 +17475,7 @@
         <v>4588.9531764893181</v>
       </c>
     </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C64" s="4" t="s">
         <v>72</v>
       </c>
@@ -17476,7 +17532,7 @@
         <v>2437.1345306322473</v>
       </c>
     </row>
-    <row r="65" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C65" s="4" t="s">
         <v>73</v>
       </c>
@@ -17533,7 +17589,7 @@
         <v>10481.069312010164</v>
       </c>
     </row>
-    <row r="66" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C66" s="4" t="s">
         <v>74</v>
       </c>
@@ -17590,7 +17646,7 @@
         <v>8743.6842854114948</v>
       </c>
     </row>
-    <row r="67" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C67" s="4" t="s">
         <v>75</v>
       </c>
@@ -17647,7 +17703,7 @@
         <v>9970.2578724433988</v>
       </c>
     </row>
-    <row r="68" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C68" s="4" t="s">
         <v>76</v>
       </c>
@@ -17704,7 +17760,7 @@
         <v>10232.788399580008</v>
       </c>
     </row>
-    <row r="69" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C69" s="4" t="s">
         <v>77</v>
       </c>
@@ -17761,7 +17817,7 @@
         <v>1750.1798244486563</v>
       </c>
     </row>
-    <row r="70" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C70" s="4" t="s">
         <v>78</v>
       </c>
@@ -17818,7 +17874,7 @@
         <v>7942.7130630920874</v>
       </c>
     </row>
-    <row r="71" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C71" s="4" t="s">
         <v>79</v>
       </c>
@@ -17875,7 +17931,7 @@
         <v>4724.5273027151707</v>
       </c>
     </row>
-    <row r="72" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C72" s="4" t="s">
         <v>80</v>
       </c>
@@ -17932,7 +17988,7 @@
         <v>9753.7217512272036</v>
       </c>
     </row>
-    <row r="73" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C73" s="4" t="s">
         <v>81</v>
       </c>
@@ -17989,7 +18045,7 @@
         <v>8434.8091173135035</v>
       </c>
     </row>
-    <row r="74" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C74" s="4" t="s">
         <v>82</v>
       </c>
@@ -18046,7 +18102,7 @@
         <v>7501.1249484992586</v>
       </c>
     </row>
-    <row r="75" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C75" s="4" t="s">
         <v>83</v>
       </c>
@@ -18103,7 +18159,7 @@
         <v>9163.9719280215795</v>
       </c>
     </row>
-    <row r="76" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C76" s="4" t="s">
         <v>84</v>
       </c>
@@ -18160,7 +18216,7 @@
         <v>7086.3685708229896</v>
       </c>
     </row>
-    <row r="77" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C77" s="4" t="s">
         <v>85</v>
       </c>
@@ -18217,7 +18273,7 @@
         <v>4592.1858980997204</v>
       </c>
     </row>
-    <row r="78" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C78" s="4" t="s">
         <v>86</v>
       </c>
@@ -18274,7 +18330,7 @@
         <v>10258.488848536392</v>
       </c>
     </row>
-    <row r="79" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C79" s="4" t="s">
         <v>87</v>
       </c>
@@ -18331,7 +18387,7 @@
         <v>2701.9487273423001</v>
       </c>
     </row>
-    <row r="80" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C80" s="4" t="s">
         <v>88</v>
       </c>
@@ -18388,7 +18444,7 @@
         <v>3569.822756985348</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C81" s="4" t="s">
         <v>89</v>
       </c>
@@ -18445,7 +18501,7 @@
         <v>10134.138419752853</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C82" s="4" t="s">
         <v>90</v>
       </c>
@@ -18502,7 +18558,7 @@
         <v>3113.8979039294645</v>
       </c>
     </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C83" s="4" t="s">
         <v>91</v>
       </c>
@@ -18559,7 +18615,7 @@
         <v>4543.1984437049832</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C84" s="4" t="s">
         <v>92</v>
       </c>
@@ -18616,7 +18672,7 @@
         <v>7723.130344127072</v>
       </c>
     </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C85" s="4" t="s">
         <v>93</v>
       </c>
@@ -18673,7 +18729,7 @@
         <v>4834.7265881524509</v>
       </c>
     </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C86" s="4" t="s">
         <v>94</v>
       </c>
@@ -18730,7 +18786,7 @@
         <v>10033.737786543439</v>
       </c>
     </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C87" s="4" t="s">
         <v>95</v>
       </c>
@@ -18787,7 +18843,7 @@
         <v>3225.8995744388085</v>
       </c>
     </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C88" s="4" t="s">
         <v>96</v>
       </c>
@@ -18844,7 +18900,7 @@
         <v>7555.5955141811282</v>
       </c>
     </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C89" s="4" t="s">
         <v>97</v>
       </c>
@@ -18901,7 +18957,7 @@
         <v>3591.2741577393172</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C90" s="4" t="s">
         <v>98</v>
       </c>
@@ -18958,7 +19014,7 @@
         <v>3482.7469760375097</v>
       </c>
     </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C91" s="4" t="s">
         <v>99</v>
       </c>
@@ -19015,7 +19071,7 @@
         <v>10782.871021489322</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C92" s="4" t="s">
         <v>100</v>
       </c>
@@ -19072,7 +19128,7 @@
         <v>4094.640948888351</v>
       </c>
     </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C93" s="4" t="s">
         <v>101</v>
       </c>
@@ -19129,7 +19185,7 @@
         <v>9321.4680642582243</v>
       </c>
     </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C94" s="4" t="s">
         <v>102</v>
       </c>
@@ -19186,7 +19242,7 @@
         <v>844.21346157963853</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C95" s="4" t="s">
         <v>103</v>
       </c>
@@ -19243,7 +19299,7 @@
         <v>6596.6109236639459</v>
       </c>
     </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C96" s="4" t="s">
         <v>104</v>
       </c>
@@ -19300,7 +19356,7 @@
         <v>9495.806437901716</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C97" s="4" t="s">
         <v>105</v>
       </c>
@@ -19357,7 +19413,7 @@
         <v>10700.949681993399</v>
       </c>
     </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C98" s="4" t="s">
         <v>106</v>
       </c>
@@ -19414,7 +19470,7 @@
         <v>8932.3314235174039</v>
       </c>
     </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C99" s="4" t="s">
         <v>107</v>
       </c>
@@ -19471,7 +19527,7 @@
         <v>7651.7511718194874</v>
       </c>
     </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C100" s="4" t="s">
         <v>108</v>
       </c>
@@ -19528,7 +19584,7 @@
         <v>2921.9513879831356</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C101" s="4" t="s">
         <v>109</v>
       </c>
@@ -19585,7 +19641,7 @@
         <v>2755.1289785106783</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C102" s="4" t="s">
         <v>110</v>
       </c>
@@ -19642,7 +19698,7 @@
         <v>7035.9044243079998</v>
       </c>
     </row>
-    <row r="104" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C104" s="8" t="s">
         <v>339</v>
       </c>
@@ -19684,7 +19740,7 @@
       </c>
       <c r="V104" s="9"/>
     </row>
-    <row r="105" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C105" s="10" cm="1">
         <f t="array" ref="C105:D109">LINEST(H3:H102,$E$3:$E$102,1,1)</f>
         <v>11.002207636744096</v>
@@ -19756,7 +19812,7 @@
         <v>114.52743573787575</v>
       </c>
     </row>
-    <row r="106" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C106" s="10">
         <v>2.8746203710838789E-3</v>
       </c>
@@ -19818,7 +19874,7 @@
         <v>1.6866505513277985</v>
       </c>
     </row>
-    <row r="107" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C107" s="10">
         <v>0.99999331002500658</v>
       </c>
@@ -19880,7 +19936,7 @@
         <v>7.7491532903948492</v>
       </c>
     </row>
-    <row r="108" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C108" s="10">
         <v>14648686.20266065</v>
       </c>
@@ -19942,7 +19998,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="109" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C109" s="12">
         <v>916700720.17655551</v>
       </c>
@@ -20004,7 +20060,7 @@
         <v>5884.8389183676572</v>
       </c>
     </row>
-    <row r="111" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C111" t="s">
         <v>351</v>
       </c>
@@ -20015,7 +20071,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="112" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C112" s="4"/>
       <c r="F112" t="s">
         <v>354</v>
@@ -20024,7 +20080,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B113" s="14"/>
       <c r="C113" s="15" t="s">
         <v>354</v>
@@ -20052,7 +20108,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B114" s="10" t="s">
         <v>357</v>
       </c>
@@ -20081,7 +20137,7 @@
         <v>8.5798335111756572</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B115" s="10" t="s">
         <v>352</v>
       </c>
@@ -20110,7 +20166,7 @@
         <v>7.7491532903948492</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B116" s="10" t="s">
         <v>353</v>
       </c>
@@ -20139,7 +20195,7 @@
         <v>9.6989610537075688</v>
       </c>
     </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B117" s="12" t="s">
         <v>356</v>
       </c>
@@ -20168,7 +20224,7 @@
         <v>1.9498077633127195</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C120" s="18" t="s">
         <v>362</v>
       </c>
@@ -20180,7 +20236,7 @@
       <c r="I120" s="18"/>
       <c r="J120" s="18"/>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C121" s="18"/>
       <c r="D121" s="18"/>
       <c r="E121" s="18"/>
@@ -20190,7 +20246,7 @@
       <c r="I121" s="18"/>
       <c r="J121" s="18"/>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C122" s="18"/>
       <c r="D122" s="18"/>
       <c r="E122" s="18"/>
@@ -20211,12 +20267,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:V122"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>213</v>
       </c>
@@ -20224,7 +20280,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="H2" t="s">
         <v>329</v>
@@ -20257,7 +20313,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -20323,7 +20379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -20389,7 +20445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -20455,7 +20511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
@@ -20515,7 +20571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
@@ -20575,7 +20631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C8" s="4" t="s">
         <v>16</v>
       </c>
@@ -20635,7 +20691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C9" s="4" t="s">
         <v>17</v>
       </c>
@@ -20695,7 +20751,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C10" s="4" t="s">
         <v>18</v>
       </c>
@@ -20755,7 +20811,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C11" s="4" t="s">
         <v>19</v>
       </c>
@@ -20815,7 +20871,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
         <v>20</v>
       </c>
@@ -20875,7 +20931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C13" s="4" t="s">
         <v>21</v>
       </c>
@@ -20935,7 +20991,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
@@ -20995,7 +21051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C15" s="4" t="s">
         <v>23</v>
       </c>
@@ -21055,7 +21111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C16" s="4" t="s">
         <v>24</v>
       </c>
@@ -21115,7 +21171,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C17" s="4" t="s">
         <v>25</v>
       </c>
@@ -21175,7 +21231,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C18" s="4" t="s">
         <v>26</v>
       </c>
@@ -21235,7 +21291,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C19" s="4" t="s">
         <v>27</v>
       </c>
@@ -21295,7 +21351,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C20" s="4" t="s">
         <v>28</v>
       </c>
@@ -21355,7 +21411,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C21" s="4" t="s">
         <v>29</v>
       </c>
@@ -21415,7 +21471,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C22" s="4" t="s">
         <v>30</v>
       </c>
@@ -21475,7 +21531,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C23" s="4" t="s">
         <v>31</v>
       </c>
@@ -21535,7 +21591,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C24" s="4" t="s">
         <v>32</v>
       </c>
@@ -21595,7 +21651,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C25" s="4" t="s">
         <v>33</v>
       </c>
@@ -21655,7 +21711,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C26" s="4" t="s">
         <v>34</v>
       </c>
@@ -21715,7 +21771,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C27" s="4" t="s">
         <v>35</v>
       </c>
@@ -21775,7 +21831,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C28" s="4" t="s">
         <v>36</v>
       </c>
@@ -21835,7 +21891,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C29" s="4" t="s">
         <v>37</v>
       </c>
@@ -21895,7 +21951,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C30" s="4" t="s">
         <v>38</v>
       </c>
@@ -21955,7 +22011,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C31" s="4" t="s">
         <v>39</v>
       </c>
@@ -22015,7 +22071,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C32" s="4" t="s">
         <v>40</v>
       </c>
@@ -22075,7 +22131,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C33" s="4" t="s">
         <v>41</v>
       </c>
@@ -22135,7 +22191,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C34" s="4" t="s">
         <v>42</v>
       </c>
@@ -22195,7 +22251,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C35" s="4" t="s">
         <v>43</v>
       </c>
@@ -22255,7 +22311,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C36" s="4" t="s">
         <v>44</v>
       </c>
@@ -22315,7 +22371,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C37" s="4" t="s">
         <v>45</v>
       </c>
@@ -22375,7 +22431,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C38" s="4" t="s">
         <v>46</v>
       </c>
@@ -22435,7 +22491,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>47</v>
       </c>
@@ -22495,7 +22551,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>48</v>
       </c>
@@ -22555,7 +22611,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C41" s="4" t="s">
         <v>49</v>
       </c>
@@ -22615,7 +22671,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C42" s="4" t="s">
         <v>50</v>
       </c>
@@ -22675,7 +22731,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C43" s="4" t="s">
         <v>51</v>
       </c>
@@ -22735,7 +22791,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C44" s="4" t="s">
         <v>52</v>
       </c>
@@ -22795,7 +22851,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C45" s="4" t="s">
         <v>53</v>
       </c>
@@ -22855,7 +22911,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C46" s="4" t="s">
         <v>54</v>
       </c>
@@ -22915,7 +22971,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C47" s="4" t="s">
         <v>55</v>
       </c>
@@ -22975,7 +23031,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C48" s="4" t="s">
         <v>56</v>
       </c>
@@ -23035,7 +23091,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C49" s="4" t="s">
         <v>57</v>
       </c>
@@ -23095,7 +23151,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C50" s="4" t="s">
         <v>58</v>
       </c>
@@ -23155,7 +23211,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C51" s="4" t="s">
         <v>59</v>
       </c>
@@ -23215,7 +23271,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C52" s="4" t="s">
         <v>60</v>
       </c>
@@ -23275,7 +23331,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C53" s="4" t="s">
         <v>61</v>
       </c>
@@ -23335,7 +23391,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C54" s="4" t="s">
         <v>62</v>
       </c>
@@ -23395,7 +23451,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C55" s="4" t="s">
         <v>63</v>
       </c>
@@ -23455,7 +23511,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C56" s="4" t="s">
         <v>64</v>
       </c>
@@ -23515,7 +23571,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C57" s="4" t="s">
         <v>65</v>
       </c>
@@ -23575,7 +23631,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C58" s="4" t="s">
         <v>66</v>
       </c>
@@ -23635,7 +23691,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C59" s="4" t="s">
         <v>67</v>
       </c>
@@ -23695,7 +23751,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C60" s="4" t="s">
         <v>68</v>
       </c>
@@ -23755,7 +23811,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C61" s="4" t="s">
         <v>69</v>
       </c>
@@ -23815,7 +23871,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C62" s="4" t="s">
         <v>70</v>
       </c>
@@ -23875,7 +23931,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C63" s="4" t="s">
         <v>71</v>
       </c>
@@ -23935,7 +23991,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C64" s="4" t="s">
         <v>72</v>
       </c>
@@ -23995,7 +24051,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C65" s="4" t="s">
         <v>73</v>
       </c>
@@ -24055,7 +24111,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C66" s="4" t="s">
         <v>74</v>
       </c>
@@ -24115,7 +24171,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C67" s="4" t="s">
         <v>75</v>
       </c>
@@ -24175,7 +24231,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C68" s="4" t="s">
         <v>76</v>
       </c>
@@ -24235,7 +24291,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C69" s="4" t="s">
         <v>77</v>
       </c>
@@ -24295,7 +24351,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C70" s="4" t="s">
         <v>78</v>
       </c>
@@ -24355,7 +24411,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C71" s="4" t="s">
         <v>79</v>
       </c>
@@ -24415,7 +24471,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C72" s="4" t="s">
         <v>80</v>
       </c>
@@ -24475,7 +24531,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C73" s="4" t="s">
         <v>81</v>
       </c>
@@ -24535,7 +24591,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C74" s="4" t="s">
         <v>82</v>
       </c>
@@ -24595,7 +24651,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C75" s="4" t="s">
         <v>83</v>
       </c>
@@ -24655,7 +24711,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C76" s="4" t="s">
         <v>84</v>
       </c>
@@ -24715,7 +24771,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C77" s="4" t="s">
         <v>85</v>
       </c>
@@ -24775,7 +24831,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C78" s="4" t="s">
         <v>86</v>
       </c>
@@ -24835,7 +24891,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C79" s="4" t="s">
         <v>87</v>
       </c>
@@ -24895,7 +24951,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C80" s="4" t="s">
         <v>88</v>
       </c>
@@ -24955,7 +25011,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C81" s="4" t="s">
         <v>89</v>
       </c>
@@ -25015,7 +25071,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C82" s="4" t="s">
         <v>90</v>
       </c>
@@ -25075,7 +25131,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C83" s="4" t="s">
         <v>91</v>
       </c>
@@ -25135,7 +25191,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C84" s="4" t="s">
         <v>92</v>
       </c>
@@ -25195,7 +25251,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C85" s="4" t="s">
         <v>93</v>
       </c>
@@ -25255,7 +25311,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C86" s="4" t="s">
         <v>94</v>
       </c>
@@ -25315,7 +25371,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C87" s="4" t="s">
         <v>95</v>
       </c>
@@ -25375,7 +25431,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C88" s="4" t="s">
         <v>96</v>
       </c>
@@ -25435,7 +25491,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C89" s="4" t="s">
         <v>97</v>
       </c>
@@ -25495,7 +25551,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C90" s="4" t="s">
         <v>98</v>
       </c>
@@ -25555,7 +25611,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C91" s="4" t="s">
         <v>99</v>
       </c>
@@ -25615,7 +25671,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C92" s="4" t="s">
         <v>100</v>
       </c>
@@ -25675,7 +25731,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C93" s="4" t="s">
         <v>101</v>
       </c>
@@ -25735,7 +25791,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C94" s="4" t="s">
         <v>102</v>
       </c>
@@ -25795,7 +25851,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C95" s="4" t="s">
         <v>103</v>
       </c>
@@ -25855,7 +25911,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C96" s="4" t="s">
         <v>104</v>
       </c>
@@ -25915,7 +25971,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C97" s="4" t="s">
         <v>105</v>
       </c>
@@ -25975,7 +26031,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C98" s="4" t="s">
         <v>106</v>
       </c>
@@ -26035,7 +26091,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C99" s="4" t="s">
         <v>107</v>
       </c>
@@ -26095,7 +26151,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C100" s="4" t="s">
         <v>108</v>
       </c>
@@ -26155,7 +26211,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C101" s="4" t="s">
         <v>109</v>
       </c>
@@ -26215,7 +26271,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C102" s="4" t="s">
         <v>110</v>
       </c>
@@ -26275,7 +26331,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="104" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C104" s="8" t="s">
         <v>339</v>
       </c>
@@ -26317,7 +26373,7 @@
       </c>
       <c r="V104" s="9"/>
     </row>
-    <row r="105" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C105" s="10" cm="1">
         <f t="array" ref="C105:D109">LINEST(H3:H102,$E$3:$E$102,1,1)</f>
         <v>11.155665423963281</v>
@@ -26389,7 +26445,7 @@
         <v>99.350713195671233</v>
       </c>
     </row>
-    <row r="106" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C106" s="10">
         <v>0.19486030187477535</v>
       </c>
@@ -26451,7 +26507,7 @@
         <v>87.887463658500579</v>
       </c>
     </row>
-    <row r="107" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C107" s="10">
         <v>0.97096736269512951</v>
       </c>
@@ -26513,7 +26569,7 @@
         <v>403.79047554194022</v>
       </c>
     </row>
-    <row r="108" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C108" s="10">
         <v>3277.5114621832709</v>
       </c>
@@ -26575,7 +26631,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="109" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C109" s="12">
         <v>942451174.77896631</v>
       </c>
@@ -26637,7 +26693,7 @@
         <v>15978581.317561852</v>
       </c>
     </row>
-    <row r="111" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C111" t="s">
         <v>351</v>
       </c>
@@ -26648,10 +26704,10 @@
         <v>359</v>
       </c>
     </row>
-    <row r="112" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C112" s="4"/>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" s="14"/>
       <c r="C113" s="15" t="s">
         <v>354</v>
@@ -26676,7 +26732,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" s="10" t="s">
         <v>357</v>
       </c>
@@ -26708,7 +26764,7 @@
         <v>14.39984534618543</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" s="10" t="s">
         <v>352</v>
       </c>
@@ -26734,7 +26790,7 @@
         <v>12.591319651784033</v>
       </c>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" s="10" t="s">
         <v>353</v>
       </c>
@@ -26760,7 +26816,7 @@
         <v>16.938115126434241</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" s="12" t="s">
         <v>356</v>
       </c>
@@ -26786,7 +26842,7 @@
         <v>4.3467954746502073</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C120" s="18" t="s">
         <v>363</v>
       </c>
@@ -26798,7 +26854,7 @@
       <c r="I120" s="18"/>
       <c r="J120" s="18"/>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C121" s="18"/>
       <c r="D121" s="18"/>
       <c r="E121" s="18"/>
@@ -26808,7 +26864,7 @@
       <c r="I121" s="18"/>
       <c r="J121" s="18"/>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C122" s="18"/>
       <c r="D122" s="18"/>
       <c r="E122" s="18"/>
@@ -26829,13 +26885,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AD122"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="19.109375" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>214</v>
       </c>
@@ -26849,7 +26905,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="H2" t="s">
         <v>329</v>
@@ -26882,7 +26938,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -26988,7 +27044,7 @@
         <v>-8.5197666521708015</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -27094,7 +27150,7 @@
         <v>-2.1491894131031599</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -27200,7 +27256,7 @@
         <v>-3.1799987709746356</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>349</v>
       </c>
@@ -27306,7 +27362,7 @@
         <v>-1.457422342809878</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>350</v>
       </c>
@@ -27412,7 +27468,7 @@
         <v>3.8758376774694625</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C8" s="4" t="s">
         <v>16</v>
       </c>
@@ -27512,7 +27568,7 @@
         <v>4.6892744620663507</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C9" s="4" t="s">
         <v>17</v>
       </c>
@@ -27612,7 +27668,7 @@
         <v>2.936772851569458</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C10" s="4" t="s">
         <v>18</v>
       </c>
@@ -27712,7 +27768,7 @@
         <v>-1.9106637871857401</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C11" s="4" t="s">
         <v>19</v>
       </c>
@@ -27812,7 +27868,7 @@
         <v>7.2972374809410878E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
         <v>20</v>
       </c>
@@ -27912,7 +27968,7 @@
         <v>-0.84454133020273014</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C13" s="4" t="s">
         <v>21</v>
       </c>
@@ -28012,7 +28068,7 @@
         <v>-0.7983649141785063</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
@@ -28112,7 +28168,7 @@
         <v>-0.48904508109792733</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C15" s="4" t="s">
         <v>23</v>
       </c>
@@ -28212,7 +28268,7 @@
         <v>-1.2199283233593761</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C16" s="4" t="s">
         <v>24</v>
       </c>
@@ -28312,7 +28368,7 @@
         <v>2.9691385058927615</v>
       </c>
     </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C17" s="4" t="s">
         <v>25</v>
       </c>
@@ -28412,7 +28468,7 @@
         <v>1.0846369355106407</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C18" s="4" t="s">
         <v>26</v>
       </c>
@@ -28512,7 +28568,7 @@
         <v>0.16483951299472976</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C19" s="4" t="s">
         <v>27</v>
       </c>
@@ -28612,7 +28668,7 @@
         <v>1.339521059551152</v>
       </c>
     </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C20" s="4" t="s">
         <v>28</v>
       </c>
@@ -28712,7 +28768,7 @@
         <v>-1.3953199501759994</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C21" s="4" t="s">
         <v>29</v>
       </c>
@@ -28812,7 +28868,7 @@
         <v>4.0611982923626906</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C22" s="4" t="s">
         <v>30</v>
       </c>
@@ -28912,7 +28968,7 @@
         <v>4.3117005339612717</v>
       </c>
     </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C23" s="4" t="s">
         <v>31</v>
       </c>
@@ -29012,7 +29068,7 @@
         <v>-0.8443976764381631</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C24" s="4" t="s">
         <v>32</v>
       </c>
@@ -29112,7 +29168,7 @@
         <v>3.1941203525499091</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C25" s="4" t="s">
         <v>33</v>
       </c>
@@ -29212,7 +29268,7 @@
         <v>-2.6562781985628128</v>
       </c>
     </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C26" s="4" t="s">
         <v>34</v>
       </c>
@@ -29312,7 +29368,7 @@
         <v>2.3899116213543952</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C27" s="4" t="s">
         <v>35</v>
       </c>
@@ -29412,7 +29468,7 @@
         <v>-0.94315936756349839</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C28" s="4" t="s">
         <v>36</v>
       </c>
@@ -29512,7 +29568,7 @@
         <v>-0.81415450562504921</v>
       </c>
     </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C29" s="4" t="s">
         <v>37</v>
       </c>
@@ -29612,7 +29668,7 @@
         <v>1.0687461573338795</v>
       </c>
     </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C30" s="4" t="s">
         <v>38</v>
       </c>
@@ -29712,7 +29768,7 @@
         <v>4.4385746273881157</v>
       </c>
     </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C31" s="4" t="s">
         <v>39</v>
       </c>
@@ -29812,7 +29868,7 @@
         <v>0.68333152447155943</v>
       </c>
     </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C32" s="4" t="s">
         <v>40</v>
       </c>
@@ -29912,7 +29968,7 @@
         <v>-3.9489982751627486</v>
       </c>
     </row>
-    <row r="33" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C33" s="4" t="s">
         <v>41</v>
       </c>
@@ -30012,7 +30068,7 @@
         <v>-10.097632876572247</v>
       </c>
     </row>
-    <row r="34" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C34" s="4" t="s">
         <v>42</v>
       </c>
@@ -30112,7 +30168,7 @@
         <v>-5.1189316585825528</v>
       </c>
     </row>
-    <row r="35" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C35" s="4" t="s">
         <v>43</v>
       </c>
@@ -30212,7 +30268,7 @@
         <v>-0.71241169298546181</v>
       </c>
     </row>
-    <row r="36" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C36" s="4" t="s">
         <v>44</v>
       </c>
@@ -30312,7 +30368,7 @@
         <v>3.1982313247676295</v>
       </c>
     </row>
-    <row r="37" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C37" s="4" t="s">
         <v>45</v>
       </c>
@@ -30412,7 +30468,7 @@
         <v>0.67775091788437258</v>
       </c>
     </row>
-    <row r="38" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C38" s="4" t="s">
         <v>46</v>
       </c>
@@ -30512,7 +30568,7 @@
         <v>3.2959178565532623</v>
       </c>
     </row>
-    <row r="39" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>47</v>
       </c>
@@ -30612,7 +30668,7 @@
         <v>3.2515504278648506</v>
       </c>
     </row>
-    <row r="40" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>48</v>
       </c>
@@ -30712,7 +30768,7 @@
         <v>2.4147163929853521</v>
       </c>
     </row>
-    <row r="41" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C41" s="4" t="s">
         <v>49</v>
       </c>
@@ -30812,7 +30868,7 @@
         <v>-0.80826850904999636</v>
       </c>
     </row>
-    <row r="42" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C42" s="4" t="s">
         <v>50</v>
       </c>
@@ -30912,7 +30968,7 @@
         <v>-2.4460089771608375</v>
       </c>
     </row>
-    <row r="43" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C43" s="4" t="s">
         <v>51</v>
       </c>
@@ -31012,7 +31068,7 @@
         <v>6.4538583901445143</v>
       </c>
     </row>
-    <row r="44" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C44" s="4" t="s">
         <v>52</v>
       </c>
@@ -31112,7 +31168,7 @@
         <v>2.2882283446886458</v>
       </c>
     </row>
-    <row r="45" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C45" s="4" t="s">
         <v>53</v>
       </c>
@@ -31212,7 +31268,7 @@
         <v>-9.9800345234166699E-3</v>
       </c>
     </row>
-    <row r="46" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C46" s="4" t="s">
         <v>54</v>
       </c>
@@ -31312,7 +31368,7 @@
         <v>0.80535270899231248</v>
       </c>
     </row>
-    <row r="47" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C47" s="4" t="s">
         <v>55</v>
       </c>
@@ -31412,7 +31468,7 @@
         <v>-2.104050205162844</v>
       </c>
     </row>
-    <row r="48" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C48" s="4" t="s">
         <v>56</v>
       </c>
@@ -31512,7 +31568,7 @@
         <v>-4.1122860538967076</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C49" s="4" t="s">
         <v>57</v>
       </c>
@@ -31612,7 +31668,7 @@
         <v>-5.9867290169679617</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C50" s="4" t="s">
         <v>58</v>
       </c>
@@ -31712,7 +31768,7 @@
         <v>-4.1928163529975135</v>
       </c>
     </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C51" s="4" t="s">
         <v>59</v>
       </c>
@@ -31812,7 +31868,7 @@
         <v>-2.2664404847319601</v>
       </c>
     </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C52" s="4" t="s">
         <v>60</v>
       </c>
@@ -31912,7 +31968,7 @@
         <v>-0.12606172577992036</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C53" s="4" t="s">
         <v>61</v>
       </c>
@@ -32012,7 +32068,7 @@
         <v>-0.65352939296305157</v>
       </c>
     </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C54" s="4" t="s">
         <v>62</v>
       </c>
@@ -32112,7 +32168,7 @@
         <v>-1.9098267330265557</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C55" s="4" t="s">
         <v>63</v>
       </c>
@@ -32212,7 +32268,7 @@
         <v>-2.635011560414636</v>
       </c>
     </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C56" s="4" t="s">
         <v>64</v>
       </c>
@@ -32312,7 +32368,7 @@
         <v>-5.0286397936361364</v>
       </c>
     </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C57" s="4" t="s">
         <v>65</v>
       </c>
@@ -32412,7 +32468,7 @@
         <v>0.58676599792304973</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C58" s="4" t="s">
         <v>66</v>
       </c>
@@ -32512,7 +32568,7 @@
         <v>6.3317219201044939E-2</v>
       </c>
     </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C59" s="4" t="s">
         <v>67</v>
       </c>
@@ -32612,7 +32668,7 @@
         <v>-2.2329286281319627</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C60" s="4" t="s">
         <v>68</v>
       </c>
@@ -32712,7 +32768,7 @@
         <v>-4.0239233342731513</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C61" s="4" t="s">
         <v>69</v>
       </c>
@@ -32812,7 +32868,7 @@
         <v>-3.953055387981526</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C62" s="4" t="s">
         <v>70</v>
       </c>
@@ -32912,7 +32968,7 @@
         <v>0.38225363626758968</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C63" s="4" t="s">
         <v>71</v>
       </c>
@@ -33012,7 +33068,7 @@
         <v>-0.49114768542682552</v>
       </c>
     </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C64" s="4" t="s">
         <v>72</v>
       </c>
@@ -33112,7 +33168,7 @@
         <v>0.46593636803569838</v>
       </c>
     </row>
-    <row r="65" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C65" s="4" t="s">
         <v>73</v>
       </c>
@@ -33212,7 +33268,7 @@
         <v>1.9227388540725625</v>
       </c>
     </row>
-    <row r="66" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C66" s="4" t="s">
         <v>74</v>
       </c>
@@ -33312,7 +33368,7 @@
         <v>-0.81053543579879073</v>
       </c>
     </row>
-    <row r="67" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C67" s="4" t="s">
         <v>75</v>
       </c>
@@ -33412,7 +33468,7 @@
         <v>-0.3193102367664587</v>
       </c>
     </row>
-    <row r="68" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C68" s="4" t="s">
         <v>76</v>
       </c>
@@ -33512,7 +33568,7 @@
         <v>-0.56352192504738419</v>
       </c>
     </row>
-    <row r="69" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C69" s="4" t="s">
         <v>77</v>
       </c>
@@ -33612,7 +33668,7 @@
         <v>6.1115138536950715</v>
       </c>
     </row>
-    <row r="70" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C70" s="4" t="s">
         <v>78</v>
       </c>
@@ -33712,7 +33768,7 @@
         <v>1.9601112908766658</v>
       </c>
     </row>
-    <row r="71" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C71" s="4" t="s">
         <v>79</v>
       </c>
@@ -33812,7 +33868,7 @@
         <v>5.1558232171618874</v>
       </c>
     </row>
-    <row r="72" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C72" s="4" t="s">
         <v>80</v>
       </c>
@@ -33912,7 +33968,7 @@
         <v>3.8184953509821571</v>
       </c>
     </row>
-    <row r="73" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C73" s="4" t="s">
         <v>81</v>
       </c>
@@ -34012,7 +34068,7 @@
         <v>-0.1543798866744146</v>
       </c>
     </row>
-    <row r="74" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C74" s="4" t="s">
         <v>82</v>
       </c>
@@ -34112,7 +34168,7 @@
         <v>5.6311262230823287</v>
       </c>
     </row>
-    <row r="75" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C75" s="4" t="s">
         <v>83</v>
       </c>
@@ -34212,7 +34268,7 @@
         <v>1.8062057854010045</v>
       </c>
     </row>
-    <row r="76" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C76" s="4" t="s">
         <v>84</v>
       </c>
@@ -34312,7 +34368,7 @@
         <v>0.35929316703037228</v>
       </c>
     </row>
-    <row r="77" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C77" s="4" t="s">
         <v>85</v>
       </c>
@@ -34412,7 +34468,7 @@
         <v>0.57494595008864002</v>
       </c>
     </row>
-    <row r="78" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C78" s="4" t="s">
         <v>86</v>
       </c>
@@ -34512,7 +34568,7 @@
         <v>-2.549577512825099</v>
       </c>
     </row>
-    <row r="79" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C79" s="4" t="s">
         <v>87</v>
       </c>
@@ -34612,7 +34668,7 @@
         <v>-0.29187964231251051</v>
       </c>
     </row>
-    <row r="80" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C80" s="4" t="s">
         <v>88</v>
       </c>
@@ -34712,7 +34768,7 @@
         <v>0.46164584062639502</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C81" s="4" t="s">
         <v>89</v>
       </c>
@@ -34812,7 +34868,7 @@
         <v>-5.6370495402394472E-2</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C82" s="4" t="s">
         <v>90</v>
       </c>
@@ -34912,7 +34968,7 @@
         <v>-1.0622172712129971</v>
       </c>
     </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C83" s="4" t="s">
         <v>91</v>
       </c>
@@ -35012,7 +35068,7 @@
         <v>-1.7982940672787486</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C84" s="4" t="s">
         <v>92</v>
       </c>
@@ -35112,7 +35168,7 @@
         <v>-1.8556989912820339</v>
       </c>
     </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C85" s="4" t="s">
         <v>93</v>
       </c>
@@ -35212,7 +35268,7 @@
         <v>-0.35232011149073073</v>
       </c>
     </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C86" s="4" t="s">
         <v>94</v>
       </c>
@@ -35312,7 +35368,7 @@
         <v>-0.93023120793231784</v>
       </c>
     </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C87" s="4" t="s">
         <v>95</v>
       </c>
@@ -35412,7 +35468,7 @@
         <v>-0.83192412436330887</v>
       </c>
     </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C88" s="4" t="s">
         <v>96</v>
       </c>
@@ -35512,7 +35568,7 @@
         <v>-2.2174573351389086</v>
       </c>
     </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C89" s="4" t="s">
         <v>97</v>
       </c>
@@ -35612,7 +35668,7 @@
         <v>-0.68400942113040064</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C90" s="4" t="s">
         <v>98</v>
       </c>
@@ -35712,7 +35768,7 @@
         <v>4.2403206352713791</v>
       </c>
     </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C91" s="4" t="s">
         <v>99</v>
       </c>
@@ -35812,7 +35868,7 @@
         <v>1.7438341474095962</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C92" s="4" t="s">
         <v>100</v>
       </c>
@@ -35912,7 +35968,7 @@
         <v>0.41890003648845697</v>
       </c>
     </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C93" s="4" t="s">
         <v>101</v>
       </c>
@@ -36012,7 +36068,7 @@
         <v>4.0321381043190057</v>
       </c>
     </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C94" s="4" t="s">
         <v>102</v>
       </c>
@@ -36112,7 +36168,7 @@
         <v>3.4205562453723473</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C95" s="4" t="s">
         <v>103</v>
       </c>
@@ -36212,7 +36268,7 @@
         <v>-0.75274732266519639</v>
       </c>
     </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C96" s="4" t="s">
         <v>104</v>
       </c>
@@ -36312,7 +36368,7 @@
         <v>2.8924389725727289</v>
       </c>
     </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C97" s="4" t="s">
         <v>105</v>
       </c>
@@ -36412,7 +36468,7 @@
         <v>-0.57055318258054188</v>
       </c>
     </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C98" s="4" t="s">
         <v>106</v>
       </c>
@@ -36512,7 +36568,7 @@
         <v>-1.5081354188223073</v>
       </c>
     </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C99" s="4" t="s">
         <v>107</v>
       </c>
@@ -36612,7 +36668,7 @@
         <v>-3.5036771029153693</v>
       </c>
     </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C100" s="4" t="s">
         <v>108</v>
       </c>
@@ -36712,7 +36768,7 @@
         <v>-4.4347092237458021</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C101" s="4" t="s">
         <v>109</v>
       </c>
@@ -36812,7 +36868,7 @@
         <v>-1.8410284416468077</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C102" s="4" t="s">
         <v>110</v>
       </c>
@@ -36912,7 +36968,7 @@
         <v>4.7627215176596183E-2</v>
       </c>
     </row>
-    <row r="104" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C104" s="8" t="s">
         <v>339</v>
       </c>
@@ -36954,7 +37010,7 @@
       </c>
       <c r="V104" s="9"/>
     </row>
-    <row r="105" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C105" s="10" cm="1">
         <f t="array" ref="C105:D109">LINEST(H3:H102,$E$3:$E$102,1,1)</f>
         <v>11.000255798404591</v>
@@ -37026,7 +37082,7 @@
         <v>13.339655216672327</v>
       </c>
     </row>
-    <row r="106" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C106" s="10">
         <v>1.0823302076084285E-3</v>
       </c>
@@ -37088,7 +37144,7 @@
         <v>0.64423570982968048</v>
       </c>
     </row>
-    <row r="107" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C107" s="10">
         <v>0.99999905127650823</v>
       </c>
@@ -37150,7 +37206,7 @@
         <v>2.959878836008091</v>
       </c>
     </row>
-    <row r="108" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C108" s="10">
         <v>103296595.77722155</v>
       </c>
@@ -37212,7 +37268,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="109" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C109" s="12">
         <v>916375495.82883418</v>
       </c>
@@ -37274,7 +37330,7 @@
         <v>858.56650693716392</v>
       </c>
     </row>
-    <row r="111" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C111" t="s">
         <v>351</v>
       </c>
@@ -37285,7 +37341,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="112" spans="3:30" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C112" s="4"/>
       <c r="F112" t="s">
         <v>354</v>
@@ -37294,7 +37350,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B113" s="14"/>
       <c r="C113" s="15" t="s">
         <v>354</v>
@@ -37322,7 +37378,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B114" s="10" t="s">
         <v>357</v>
       </c>
@@ -37351,7 +37407,7 @@
         <v>8.5798335111756572</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B115" s="10" t="s">
         <v>352</v>
       </c>
@@ -37380,7 +37436,7 @@
         <v>7.7491532903948492</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B116" s="10" t="s">
         <v>353</v>
       </c>
@@ -37409,7 +37465,7 @@
         <v>9.6989610537075688</v>
       </c>
     </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B117" s="12" t="s">
         <v>356</v>
       </c>
@@ -37438,7 +37494,7 @@
         <v>1.9498077633127195</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C120" s="18" t="s">
         <v>364</v>
       </c>
@@ -37450,7 +37506,7 @@
       <c r="I120" s="18"/>
       <c r="J120" s="18"/>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C121" s="18"/>
       <c r="D121" s="18"/>
       <c r="E121" s="18"/>
@@ -37460,7 +37516,7 @@
       <c r="I121" s="18"/>
       <c r="J121" s="18"/>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C122" s="18"/>
       <c r="D122" s="18"/>
       <c r="E122" s="18"/>
@@ -37481,14 +37537,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AA122"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>211</v>
       </c>
@@ -37496,7 +37552,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="F2" t="s">
         <v>329</v>
@@ -37559,7 +37615,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -37662,7 +37718,7 @@
         <v>2341.9190336085157</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -37765,7 +37821,7 @@
         <v>8595.4229988209991</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -37868,7 +37924,7 @@
         <v>3086.6779162251478</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
@@ -37965,7 +38021,7 @@
         <v>9796.2997623697738</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
@@ -38062,7 +38118,7 @@
         <v>3493.137412649201</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C8" s="4" t="s">
         <v>16</v>
       </c>
@@ -38159,7 +38215,7 @@
         <v>8605.8647108138248</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C9" s="4" t="s">
         <v>17</v>
       </c>
@@ -38256,7 +38312,7 @@
         <v>10929.034013303055</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C10" s="4" t="s">
         <v>18</v>
       </c>
@@ -38353,7 +38409,7 @@
         <v>3590.6950620243151</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C11" s="4" t="s">
         <v>19</v>
       </c>
@@ -38450,7 +38506,7 @@
         <v>9981.1273664313194</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
         <v>20</v>
       </c>
@@ -38547,7 +38603,7 @@
         <v>8699.6412830215413</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C13" s="4" t="s">
         <v>21</v>
       </c>
@@ -38644,7 +38700,7 @@
         <v>1409.3513998813578</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
@@ -38741,7 +38797,7 @@
         <v>7545.744286363537</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C15" s="4" t="s">
         <v>23</v>
       </c>
@@ -38838,7 +38894,7 @@
         <v>3541.1608201324125</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C16" s="4" t="s">
         <v>24</v>
       </c>
@@ -38935,7 +38991,7 @@
         <v>7263.9235794954584</v>
       </c>
     </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C17" s="4" t="s">
         <v>25</v>
       </c>
@@ -39032,7 +39088,7 @@
         <v>4807.4011446384538</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C18" s="4" t="s">
         <v>26</v>
       </c>
@@ -39129,7 +39185,7 @@
         <v>7562.3872144083725</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C19" s="4" t="s">
         <v>27</v>
       </c>
@@ -39226,7 +39282,7 @@
         <v>8779.4141300046758</v>
       </c>
     </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C20" s="4" t="s">
         <v>28</v>
       </c>
@@ -39323,7 +39379,7 @@
         <v>5124.7046130425297</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C21" s="4" t="s">
         <v>29</v>
       </c>
@@ -39420,7 +39476,7 @@
         <v>5692.2924511439924</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C22" s="4" t="s">
         <v>30</v>
       </c>
@@ -39517,7 +39573,7 @@
         <v>7977.3632945916033</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C23" s="4" t="s">
         <v>31</v>
       </c>
@@ -39614,7 +39670,7 @@
         <v>706.84804844643804</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C24" s="4" t="s">
         <v>32</v>
       </c>
@@ -39711,7 +39767,7 @@
         <v>3292.4998219083063</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C25" s="4" t="s">
         <v>33</v>
       </c>
@@ -39808,7 +39864,7 @@
         <v>7588.5585781208356</v>
       </c>
     </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C26" s="4" t="s">
         <v>34</v>
       </c>
@@ -39905,7 +39961,7 @@
         <v>3079.2185071076092</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C27" s="4" t="s">
         <v>35</v>
       </c>
@@ -40002,7 +40058,7 @@
         <v>7716.1325198809209</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C28" s="4" t="s">
         <v>36</v>
       </c>
@@ -40099,7 +40155,7 @@
         <v>2426.1713625503471</v>
       </c>
     </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C29" s="4" t="s">
         <v>37</v>
       </c>
@@ -40196,7 +40252,7 @@
         <v>7357.1239571500337</v>
       </c>
     </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C30" s="4" t="s">
         <v>38</v>
       </c>
@@ -40293,7 +40349,7 @@
         <v>1035.7075383109768</v>
       </c>
     </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C31" s="4" t="s">
         <v>39</v>
       </c>
@@ -40390,7 +40446,7 @@
         <v>2745.4961699939886</v>
       </c>
     </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C32" s="4" t="s">
         <v>40</v>
       </c>
@@ -40487,7 +40543,7 @@
         <v>2745.8981639792328</v>
       </c>
     </row>
-    <row r="33" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C33" s="4" t="s">
         <v>41</v>
       </c>
@@ -40584,7 +40640,7 @@
         <v>1194.0048306294775</v>
       </c>
     </row>
-    <row r="34" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C34" s="4" t="s">
         <v>42</v>
       </c>
@@ -40681,7 +40737,7 @@
         <v>2054.2840732678305</v>
       </c>
     </row>
-    <row r="35" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C35" s="4" t="s">
         <v>43</v>
       </c>
@@ -40778,7 +40834,7 @@
         <v>3122.4358433469024</v>
       </c>
     </row>
-    <row r="36" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C36" s="4" t="s">
         <v>44</v>
       </c>
@@ -40875,7 +40931,7 @@
         <v>3489.268842061123</v>
       </c>
     </row>
-    <row r="37" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C37" s="4" t="s">
         <v>45</v>
       </c>
@@ -40972,7 +41028,7 @@
         <v>9732.4927897963353</v>
       </c>
     </row>
-    <row r="38" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C38" s="4" t="s">
         <v>46</v>
       </c>
@@ -41069,7 +41125,7 @@
         <v>854.65326329000527</v>
       </c>
     </row>
-    <row r="39" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>47</v>
       </c>
@@ -41166,7 +41222,7 @@
         <v>8415.2466590356489</v>
       </c>
     </row>
-    <row r="40" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>48</v>
       </c>
@@ -41263,7 +41319,7 @@
         <v>4828.845904206566</v>
       </c>
     </row>
-    <row r="41" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C41" s="4" t="s">
         <v>49</v>
       </c>
@@ -41360,7 +41416,7 @@
         <v>8272.483744578436</v>
       </c>
     </row>
-    <row r="42" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C42" s="4" t="s">
         <v>50</v>
       </c>
@@ -41457,7 +41513,7 @@
         <v>6706.5437146531767</v>
       </c>
     </row>
-    <row r="43" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C43" s="4" t="s">
         <v>51</v>
       </c>
@@ -41554,7 +41610,7 @@
         <v>8102.3323946708406</v>
       </c>
     </row>
-    <row r="44" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C44" s="4" t="s">
         <v>52</v>
       </c>
@@ -41651,7 +41707,7 @@
         <v>5793.0958142613235</v>
       </c>
     </row>
-    <row r="45" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C45" s="4" t="s">
         <v>53</v>
       </c>
@@ -41748,7 +41804,7 @@
         <v>2982.199349420247</v>
       </c>
     </row>
-    <row r="46" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C46" s="4" t="s">
         <v>54</v>
       </c>
@@ -41845,7 +41901,7 @@
         <v>8017.4510769839544</v>
       </c>
     </row>
-    <row r="47" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C47" s="4" t="s">
         <v>55</v>
       </c>
@@ -41942,7 +41998,7 @@
         <v>7068.6278864273045</v>
       </c>
     </row>
-    <row r="48" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C48" s="4" t="s">
         <v>56</v>
       </c>
@@ -42039,7 +42095,7 @@
         <v>9307.9872852084518</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C49" s="4" t="s">
         <v>57</v>
       </c>
@@ -42136,7 +42192,7 @@
         <v>10775.989495836388</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C50" s="4" t="s">
         <v>58</v>
       </c>
@@ -42233,7 +42289,7 @@
         <v>3716.0919129787508</v>
       </c>
     </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C51" s="4" t="s">
         <v>59</v>
       </c>
@@ -42330,7 +42386,7 @@
         <v>10708.398023752903</v>
       </c>
     </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C52" s="4" t="s">
         <v>60</v>
       </c>
@@ -42427,7 +42483,7 @@
         <v>1929.9214189705963</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C53" s="4" t="s">
         <v>61</v>
       </c>
@@ -42524,7 +42580,7 @@
         <v>2504.0856526134303</v>
       </c>
     </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C54" s="4" t="s">
         <v>62</v>
       </c>
@@ -42621,7 +42677,7 @@
         <v>2984.1551446176309</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C55" s="4" t="s">
         <v>63</v>
       </c>
@@ -42718,7 +42774,7 @@
         <v>3549.7062379154086</v>
       </c>
     </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C56" s="4" t="s">
         <v>64</v>
       </c>
@@ -42815,7 +42871,7 @@
         <v>4222.695766301651</v>
       </c>
     </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C57" s="4" t="s">
         <v>65</v>
       </c>
@@ -42912,7 +42968,7 @@
         <v>3258.680450941436</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C58" s="4" t="s">
         <v>66</v>
       </c>
@@ -43009,7 +43065,7 @@
         <v>3647.3626637610141</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C59" s="4" t="s">
         <v>67</v>
       </c>
@@ -43106,7 +43162,7 @@
         <v>9984.974136401026</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C60" s="4" t="s">
         <v>68</v>
       </c>
@@ -43203,7 +43259,7 @@
         <v>1669.5160357633722</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C61" s="4" t="s">
         <v>69</v>
       </c>
@@ -43300,7 +43356,7 @@
         <v>6536.9590003476769</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C62" s="4" t="s">
         <v>70</v>
       </c>
@@ -43397,7 +43453,7 @@
         <v>4332.6020413669321</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C63" s="4" t="s">
         <v>71</v>
       </c>
@@ -43494,7 +43550,7 @@
         <v>4490.6328574525251</v>
       </c>
     </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C64" s="4" t="s">
         <v>72</v>
       </c>
@@ -43591,7 +43647,7 @@
         <v>2342.6781827829109</v>
       </c>
     </row>
-    <row r="65" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C65" s="4" t="s">
         <v>73</v>
       </c>
@@ -43688,7 +43744,7 @@
         <v>10376.880111201695</v>
       </c>
     </row>
-    <row r="66" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C66" s="4" t="s">
         <v>74</v>
       </c>
@@ -43785,7 +43841,7 @@
         <v>8642.7608879463369</v>
       </c>
     </row>
-    <row r="67" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C67" s="4" t="s">
         <v>75</v>
       </c>
@@ -43882,7 +43938,7 @@
         <v>9869.1035770108283</v>
       </c>
     </row>
-    <row r="68" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C68" s="4" t="s">
         <v>76</v>
       </c>
@@ -43979,7 +44035,7 @@
         <v>10151.698979490888</v>
       </c>
     </row>
-    <row r="69" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C69" s="4" t="s">
         <v>77</v>
       </c>
@@ -44076,7 +44132,7 @@
         <v>1651.1550707515562</v>
       </c>
     </row>
-    <row r="70" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C70" s="4" t="s">
         <v>78</v>
       </c>
@@ -44173,7 +44229,7 @@
         <v>7854.5099353832775</v>
       </c>
     </row>
-    <row r="71" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C71" s="4" t="s">
         <v>79</v>
       </c>
@@ -44270,7 +44326,7 @@
         <v>4631.03289899019</v>
       </c>
     </row>
-    <row r="72" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C72" s="4" t="s">
         <v>80</v>
       </c>
@@ -44367,7 +44423,7 @@
         <v>9648.3579243689746</v>
       </c>
     </row>
-    <row r="73" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C73" s="4" t="s">
         <v>81</v>
       </c>
@@ -44464,7 +44520,7 @@
         <v>8350.5583141046518</v>
       </c>
     </row>
-    <row r="74" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C74" s="4" t="s">
         <v>82</v>
       </c>
@@ -44561,7 +44617,7 @@
         <v>7401.9024206317845</v>
       </c>
     </row>
-    <row r="75" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C75" s="4" t="s">
         <v>83</v>
       </c>
@@ -44658,7 +44714,7 @@
         <v>9061.6675939604756</v>
       </c>
     </row>
-    <row r="76" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C76" s="4" t="s">
         <v>84</v>
       </c>
@@ -44755,7 +44811,7 @@
         <v>6987.1919291055965</v>
       </c>
     </row>
-    <row r="77" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C77" s="4" t="s">
         <v>85</v>
       </c>
@@ -44852,7 +44908,7 @@
         <v>4483.9382795471611</v>
       </c>
     </row>
-    <row r="78" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C78" s="4" t="s">
         <v>86</v>
       </c>
@@ -44949,7 +45005,7 @@
         <v>10159.546208886779</v>
       </c>
     </row>
-    <row r="79" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C79" s="4" t="s">
         <v>87</v>
       </c>
@@ -45046,7 +45102,7 @@
         <v>2604.4267570703814</v>
       </c>
     </row>
-    <row r="80" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C80" s="4" t="s">
         <v>88</v>
       </c>
@@ -45143,7 +45199,7 @@
         <v>3469.3662338460563</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C81" s="4" t="s">
         <v>89</v>
       </c>
@@ -45240,7 +45296,7 @@
         <v>10030.844861405174</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C82" s="4" t="s">
         <v>90</v>
       </c>
@@ -45337,7 +45393,7 @@
         <v>3009.4069929521065</v>
       </c>
     </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C83" s="4" t="s">
         <v>91</v>
       </c>
@@ -45434,7 +45490,7 @@
         <v>4439.4839975442737</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C84" s="4" t="s">
         <v>92</v>
       </c>
@@ -45531,7 +45587,7 @@
         <v>7624.2192309744278</v>
       </c>
     </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C85" s="4" t="s">
         <v>93</v>
       </c>
@@ -45628,7 +45684,7 @@
         <v>4732.8480609519902</v>
       </c>
     </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C86" s="4" t="s">
         <v>94</v>
       </c>
@@ -45725,7 +45781,7 @@
         <v>9932.1346468807897</v>
       </c>
     </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C87" s="4" t="s">
         <v>95</v>
       </c>
@@ -45822,7 +45878,7 @@
         <v>3120.2505496063386</v>
       </c>
     </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C88" s="4" t="s">
         <v>96</v>
       </c>
@@ -45919,7 +45975,7 @@
         <v>7455.6686750718072</v>
       </c>
     </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C89" s="4" t="s">
         <v>97</v>
       </c>
@@ -46016,7 +46072,7 @@
         <v>3505.3042799411196</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C90" s="4" t="s">
         <v>98</v>
       </c>
@@ -46113,7 +46169,7 @@
         <v>3384.6728810907225</v>
       </c>
     </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C91" s="4" t="s">
         <v>99</v>
       </c>
@@ -46210,7 +46266,7 @@
         <v>10681.261086264189</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C92" s="4" t="s">
         <v>100</v>
       </c>
@@ -46307,7 +46363,7 @@
         <v>4005.8070017884311</v>
       </c>
     </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C93" s="4" t="s">
         <v>101</v>
       </c>
@@ -46404,7 +46460,7 @@
         <v>9228.2299845619127</v>
       </c>
     </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C94" s="4" t="s">
         <v>102</v>
       </c>
@@ -46501,7 +46557,7 @@
         <v>737.76071003905963</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C95" s="4" t="s">
         <v>103</v>
       </c>
@@ -46598,7 +46654,7 @@
         <v>6504.7753446020943</v>
       </c>
     </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C96" s="4" t="s">
         <v>104</v>
       </c>
@@ -46695,7 +46751,7 @@
         <v>9391.9353283177188</v>
       </c>
     </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C97" s="4" t="s">
         <v>105</v>
       </c>
@@ -46792,7 +46848,7 @@
         <v>10595.936590398225</v>
       </c>
     </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C98" s="4" t="s">
         <v>106</v>
       </c>
@@ -46889,7 +46945,7 @@
         <v>8823.2673561185366</v>
       </c>
     </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C99" s="4" t="s">
         <v>107</v>
       </c>
@@ -46986,7 +47042,7 @@
         <v>7541.8694868736202</v>
       </c>
     </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C100" s="4" t="s">
         <v>108</v>
       </c>
@@ -47083,7 +47139,7 @@
         <v>2821.2917860456218</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C101" s="4" t="s">
         <v>109</v>
       </c>
@@ -47180,7 +47236,7 @@
         <v>2658.2842869321626</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C102" s="4" t="s">
         <v>110</v>
       </c>
@@ -47277,7 +47333,7 @@
         <v>6936.5498519319999</v>
       </c>
     </row>
-    <row r="104" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C104" s="8" t="s">
         <v>339</v>
       </c>
@@ -47319,7 +47375,7 @@
       </c>
       <c r="V104" s="9"/>
     </row>
-    <row r="105" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C105" s="10" cm="1">
         <f t="array" ref="C105:D109">LINEST(R3:R102,$F$3:$F$102,1,1)</f>
         <v>10.996849635367868</v>
@@ -47391,7 +47447,7 @@
         <v>14.119330749251276</v>
       </c>
     </row>
-    <row r="106" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C106" s="10">
         <v>2.8649001903190488E-3</v>
       </c>
@@ -47453,7 +47509,7 @@
         <v>1.677319585653245</v>
       </c>
     </row>
-    <row r="107" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C107" s="10">
         <v>0.99999334871425349</v>
       </c>
@@ -47515,7 +47571,7 @@
         <v>7.7056425100233668</v>
       </c>
     </row>
-    <row r="108" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C108" s="10">
         <v>14733895.35623393</v>
       </c>
@@ -47577,7 +47633,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="109" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C109" s="12">
         <v>916266577.06148458</v>
       </c>
@@ -47639,7 +47695,7 @@
         <v>5818.938796243363</v>
       </c>
     </row>
-    <row r="111" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C111" t="s">
         <v>351</v>
       </c>
@@ -47650,7 +47706,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="112" spans="3:27" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C112" s="4"/>
       <c r="G112" t="s">
         <v>354</v>
@@ -47659,7 +47715,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B113" s="14"/>
       <c r="C113" s="15" t="s">
         <v>354</v>
@@ -47687,7 +47743,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B114" s="10" t="s">
         <v>357</v>
       </c>
@@ -47716,7 +47772,7 @@
         <v>8.5798335111756572</v>
       </c>
     </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B115" s="10" t="s">
         <v>352</v>
       </c>
@@ -47745,7 +47801,7 @@
         <v>7.7491532903948492</v>
       </c>
     </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B116" s="10" t="s">
         <v>353</v>
       </c>
@@ -47774,7 +47830,7 @@
         <v>9.6989610537075688</v>
       </c>
     </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B117" s="12" t="s">
         <v>356</v>
       </c>
@@ -47803,7 +47859,7 @@
         <v>1.9498077633127195</v>
       </c>
     </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C120" s="18" t="s">
         <v>365</v>
       </c>
@@ -47815,7 +47871,7 @@
       <c r="I120" s="18"/>
       <c r="J120" s="18"/>
     </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C121" s="18"/>
       <c r="D121" s="18"/>
       <c r="E121" s="18"/>
@@ -47825,7 +47881,7 @@
       <c r="I121" s="18"/>
       <c r="J121" s="18"/>
     </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C122" s="18"/>
       <c r="D122" s="18"/>
       <c r="E122" s="18"/>
@@ -47842,4 +47898,14 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F26064C6-2520-4796-887D-76FC95089396}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>